--- a/import_template.xlsx
+++ b/import_template.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\79132\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\79132\EMV\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23016" windowHeight="9168"/>
   </bookViews>
   <sheets>
     <sheet name="Лист2" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1620" uniqueCount="1620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="1635">
   <si>
     <t>Бренд</t>
   </si>
@@ -2111,9 +2111,6 @@
     <t>HEAT-ON</t>
   </si>
   <si>
-    <t>HANGCHA Forklift</t>
-  </si>
-  <si>
     <t>BPE</t>
   </si>
   <si>
@@ -4887,6 +4884,54 @@
   </si>
   <si>
     <t>ACE</t>
+  </si>
+  <si>
+    <t>HANGCHA</t>
+  </si>
+  <si>
+    <t>SITRAK</t>
+  </si>
+  <si>
+    <t>BEHR</t>
+  </si>
+  <si>
+    <t>Weifang</t>
+  </si>
+  <si>
+    <t>TECH</t>
+  </si>
+  <si>
+    <t>WIRAX</t>
+  </si>
+  <si>
+    <t>SEM</t>
+  </si>
+  <si>
+    <t>MAN</t>
+  </si>
+  <si>
+    <t>MANN-FILTER</t>
+  </si>
+  <si>
+    <t>Schneider Electric</t>
+  </si>
+  <si>
+    <t>Tech</t>
+  </si>
+  <si>
+    <t>Wirax</t>
+  </si>
+  <si>
+    <t>MLPD</t>
+  </si>
+  <si>
+    <t>EPE</t>
+  </si>
+  <si>
+    <t>YANTAI</t>
+  </si>
+  <si>
+    <t>Brembo</t>
   </si>
 </sst>
 </file>
@@ -5217,7 +5262,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B1621"/>
+  <dimension ref="A1:B1635"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
@@ -7867,7 +7912,7 @@
     </row>
     <row r="529" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A529" s="3" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="530" spans="1:1" x14ac:dyDescent="0.3">
@@ -8702,4631 +8747,4703 @@
     </row>
     <row r="696" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A696" s="3" t="s">
-        <v>694</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="697" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A697" s="3" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="698" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A698" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="699" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A699" s="3" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="700" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A700" s="3" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="701" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A701" s="3" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="702" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A702" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="703" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A703" s="3" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="704" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A704" s="3" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="705" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A705" s="3" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="706" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A706" s="3" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="707" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A707" s="3" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="708" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A708" s="3" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="709" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A709" s="3" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="710" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A710" s="3" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="711" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A711" s="3" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="712" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A712" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="713" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A713" s="3" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="714" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A714" s="3" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="715" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A715" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="716" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A716" s="3" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="717" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A717" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="718" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A718" s="3" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="719" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A719" s="3" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="720" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A720" s="3" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="721" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A721" s="3" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="722" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A722" s="3" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="723" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A723" s="3" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="724" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A724" s="3" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="725" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A725" s="3" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="726" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A726" s="3" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="727" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A727" s="3" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="728" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A728" s="3" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="729" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A729" s="3" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="730" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A730" s="3" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="731" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A731" s="3" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="732" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A732" s="3" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="733" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A733" s="3" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="734" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A734" s="3" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="735" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A735" s="3" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="736" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A736" s="3" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="737" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A737" s="3" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="738" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A738" s="3" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="739" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A739" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="740" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A740" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="741" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A741" s="3" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="742" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A742" s="3" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="743" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A743" s="3" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="744" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A744" s="3" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="745" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A745" s="3" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="746" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A746" s="3" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="747" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A747" s="3" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="748" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A748" s="3" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="749" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A749" s="3" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="750" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A750" s="3" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="751" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A751" s="3" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="752" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A752" s="3" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="753" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A753" s="3" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="754" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A754" s="3" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="755" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A755" s="3" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="756" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A756" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="757" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A757" s="3" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="758" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A758" s="3" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="759" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A759" s="3" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="760" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A760" s="3" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="761" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A761" s="3" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="762" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A762" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="763" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A763" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="764" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A764" s="3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="765" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A765" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="766" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A766" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="767" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A767" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="768" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A768" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="769" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A769" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="770" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A770" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="771" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A771" s="3" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="772" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A772" s="3" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="773" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A773" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="774" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A774" s="3" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="775" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A775" s="3" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="776" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A776" s="3" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="777" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A777" s="3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="778" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A778" s="3" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="779" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A779" s="3" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="780" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A780" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="781" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A781" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="782" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A782" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="783" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A783" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="784" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A784" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="785" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A785" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="786" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A786" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="787" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A787" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="788" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A788" s="3" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="789" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A789" s="3" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="790" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A790" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="791" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A791" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="792" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A792" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="793" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A793" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="794" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A794" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="795" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A795" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="796" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A796" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="797" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A797" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="798" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A798" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="799" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A799" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="800" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A800" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="801" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A801" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="802" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A802" s="3" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="803" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A803" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="804" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A804" s="3" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="805" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A805" s="3" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="806" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A806" s="3" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="807" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A807" s="3" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="808" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A808" s="3" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="809" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A809" s="3" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="810" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A810" s="3" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="811" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A811" s="3" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="812" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A812" s="3" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="813" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A813" s="3" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="814" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A814" s="3" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="815" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A815" s="3" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="816" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A816" s="3" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="817" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A817" s="3" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="818" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A818" s="3" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="819" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A819" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="820" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A820" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="821" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A821" s="3" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="822" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A822" s="3" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="823" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A823" s="3" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="824" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A824" s="3" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="825" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A825" s="3" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="826" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A826" s="3" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="827" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A827" s="3" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="828" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A828" s="3" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="829" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A829" s="3" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="830" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A830" s="3" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="831" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A831" s="3" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="832" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A832" s="3" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="833" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A833" s="3" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="834" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A834" s="3" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="835" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A835" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="836" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A836" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="837" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A837" s="3" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="838" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A838" s="3" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="839" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A839" s="3" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="840" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A840" s="3" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="841" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A841" s="3" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="842" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A842" s="3" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="843" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A843" s="3" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="844" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A844" s="3" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="845" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A845" s="3" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="846" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A846" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="847" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A847" s="3" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="848" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A848" s="3" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="849" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A849" s="3" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="850" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A850" s="3" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="851" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A851" s="3" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="852" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A852" s="3" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="853" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A853" s="3" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="854" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A854" s="3" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="855" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A855" s="3" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="856" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A856" s="3" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="857" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A857" s="3" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="858" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A858" s="3" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="859" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A859" s="3" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="860" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A860" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="861" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A861" s="3" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="862" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A862" s="3" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="863" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A863" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="864" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A864" s="3" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="865" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A865" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="866" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A866" s="3" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="867" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A867" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="868" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A868" s="3" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="869" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A869" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="870" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A870" s="3" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="871" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A871" s="3" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="872" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A872" s="3" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="873" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A873" s="3" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="874" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A874" s="3" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="875" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A875" s="3" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="876" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A876" s="3" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="877" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A877" s="3" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="878" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A878" s="3" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="879" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A879" s="3" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="880" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A880" s="3" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="881" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A881" s="3" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="882" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A882" s="3" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="883" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A883" s="3" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="884" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A884" s="3" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="885" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A885" s="3" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="886" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A886" s="3" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="887" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A887" s="3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="888" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A888" s="3" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="889" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A889" s="3" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="890" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A890" s="3" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="891" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A891" s="3" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="892" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A892" s="3" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="893" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A893" s="3" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="894" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A894" s="3" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="895" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A895" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="896" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A896" s="3" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="897" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A897" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="898" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A898" s="3" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="899" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A899" s="3" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="900" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A900" s="3" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="901" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A901" s="3" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="902" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A902" s="3" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="903" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A903" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="904" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A904" s="3" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="905" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A905" s="3" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="906" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A906" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="907" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A907" s="3" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="908" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A908" s="3" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="909" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A909" s="3" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="910" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A910" s="3" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="911" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A911" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="912" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A912" s="3" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="913" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A913" s="3" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="914" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A914" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="915" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A915" s="3" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="916" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A916" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="917" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A917" s="3" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="918" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A918" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="919" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A919" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="920" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A920" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="921" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A921" s="3" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="922" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A922" s="3" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="923" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A923" s="3" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="924" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A924" s="3" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="925" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A925" s="3" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="926" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A926" s="3" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="927" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A927" s="3" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="928" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A928" s="3" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="929" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A929" s="3" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="930" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A930" s="3" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="931" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A931" s="3" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="932" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A932" s="3" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="933" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A933" s="3" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="934" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A934" s="3" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="935" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A935" s="3" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="936" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A936" s="3" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="937" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A937" s="3" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="938" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A938" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="939" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A939" s="3" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="940" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A940" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="941" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A941" s="3" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="942" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A942" s="3" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="943" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A943" s="3" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="944" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A944" s="3" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="945" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A945" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="946" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A946" s="3" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="947" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A947" s="3" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="948" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A948" s="3" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="949" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A949" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="950" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A950" s="3" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="951" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A951" s="3" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="952" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A952" s="3" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="953" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A953" s="3" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="954" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A954" s="3" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="955" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A955" s="3" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="956" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A956" s="3" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="957" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A957" s="3" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="958" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A958" s="3" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="959" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A959" s="3" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="960" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A960" s="3" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="961" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A961" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="962" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A962" s="3" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="963" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A963" s="3" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="964" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A964" s="3" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="965" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A965" s="3" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="966" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A966" s="3" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="967" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A967" s="3" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="968" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A968" s="3" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="969" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A969" s="3" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="970" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A970" s="3" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="971" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A971" s="3" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="972" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A972" s="3" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="973" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A973" s="3" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="974" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A974" s="3" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="975" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A975" s="3" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="976" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A976" s="3" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="977" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A977" s="3" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="978" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A978" s="3" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="979" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A979" s="3" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="980" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A980" s="3" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="981" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A981" s="3" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="982" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A982" s="3" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="983" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A983" s="3" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="984" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A984" s="3" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="985" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A985" s="3" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="986" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A986" s="3" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="987" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A987" s="3" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="988" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A988" s="3" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="989" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A989" s="3" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="990" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A990" s="3" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="991" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A991" s="3" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="992" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A992" s="3" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="993" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A993" s="3" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="994" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A994" s="3" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="995" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A995" s="3" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="996" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A996" s="3" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="997" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A997" s="3" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="998" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A998" s="3" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="999" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A999" s="3" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="1000" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1000" s="3" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="1001" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1001" s="3" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="1002" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1002" s="3" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="1003" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1003" s="3" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="1004" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1004" s="3" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="1005" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1005" s="3" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="1006" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1006" s="3" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="1007" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1007" s="3" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="1008" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1008" s="3" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="1009" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1009" s="3" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="1010" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1010" s="3" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="1011" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1011" s="3" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="1012" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1012" s="3" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="1013" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1013" s="3" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="1014" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1014" s="3" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="1015" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1015" s="3" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="1016" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1016" s="3" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="1017" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1017" s="3" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="1018" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1018" s="3" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="1019" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1019" s="3" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="1020" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1020" s="3" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="1021" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1021" s="3" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="1022" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1022" s="3" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="1023" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1023" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="1024" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1024" s="3" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="1025" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1025" s="3" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="1026" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1026" s="3" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="1027" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1027" s="3" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="1028" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1028" s="3" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="1029" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1029" s="3" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="1030" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1030" s="3" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="1031" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1031" s="3" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="1032" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1032" s="3" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="1033" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1033" s="3" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="1034" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1034" s="3" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="1035" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1035" s="3" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="1036" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1036" s="3" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="1037" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1037" s="3" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="1038" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1038" s="3" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="1039" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1039" s="3" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="1040" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1040" s="3" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="1041" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1041" s="3" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="1042" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1042" s="3" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="1043" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1043" s="3" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="1044" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1044" s="3" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="1045" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1045" s="3" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="1046" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1046" s="3" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="1047" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1047" s="3" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="1048" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1048" s="3" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="1049" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1049" s="3" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="1050" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1050" s="3" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="1051" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1051" s="3" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="1052" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1052" s="3" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="1053" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1053" s="3" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="1054" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1054" s="3" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="1055" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1055" s="3" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="1056" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1056" s="3" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="1057" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1057" s="3" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1058" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1058" s="3" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="1059" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1059" s="3" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="1060" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1060" s="3" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="1061" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1061" s="3" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="1062" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1062" s="3" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="1063" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1063" s="3" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="1064" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1064" s="3" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="1065" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1065" s="3" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="1066" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1066" s="3" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="1067" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1067" s="3" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="1068" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1068" s="3" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="1069" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1069" s="3" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="1070" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1070" s="3" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="1071" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1071" s="3" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="1072" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1072" s="3" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="1073" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1073" s="3" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="1074" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1074" s="3" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="1075" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1075" s="3" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="1076" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1076" s="3" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="1077" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1077" s="3" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="1078" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1078" s="3" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="1079" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1079" s="3" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="1080" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1080" s="3" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="1081" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1081" s="3" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="1082" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1082" s="3" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="1083" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1083" s="3" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="1084" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1084" s="3" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="1085" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1085" s="3" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="1086" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1086" s="3" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="1087" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1087" s="3" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="1088" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1088" s="3" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="1089" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1089" s="3" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="1090" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1090" s="3" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="1091" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1091" s="3" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="1092" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1092" s="3" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="1093" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1093" s="3" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="1094" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1094" s="3" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="1095" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1095" s="3" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="1096" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1096" s="3" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="1097" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1097" s="3" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="1098" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1098" s="3" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="1099" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1099" s="3" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="1100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1100" s="3" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="1101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1101" s="3" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="1102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1102" s="3" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="1103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1103" s="3" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="1104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1104" s="3" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="1105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1105" s="3" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="1106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1106" s="3" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="1107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1107" s="3" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="1108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1108" s="3" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="1109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1109" s="3" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="1110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1110" s="3" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="1111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1111" s="3" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="1112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1112" s="3" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="1113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1113" s="3" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="1114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1114" s="3" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="1115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1115" s="3" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="1116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1116" s="3" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="1117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1117" s="3" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="1118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1118" s="3" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="1119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1119" s="3" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="1120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1120" s="3" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="1121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1121" s="3" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="1122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1122" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="1123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1123" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="1124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1124" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="1125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1125" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="1126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1126" s="3" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="1127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1127" s="3" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="1128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1128" s="3" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="1129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1129" s="3" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="1130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1130" s="3" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="1131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1131" s="3" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="1132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1132" s="3" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="1133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1133" s="3" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="1134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1134" s="3" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="1135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1135" s="3" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="1136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1136" s="3" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="1137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1137" s="3" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="1138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1138" s="3" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="1139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1139" s="3" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="1140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1140" s="3" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="1141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1141" s="3" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="1142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1142" s="3" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="1143" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1143" s="3" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="1144" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1144" s="3" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="1145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1145" s="3" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="1146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1146" s="3" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="1147" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1147" s="3" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="1148" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1148" s="3" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="1149" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1149" s="3" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="1150" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1150" s="3" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="1151" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1151" s="3" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="1152" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1152" s="3" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="1153" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1153" s="3" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="1154" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1154" s="3" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="1155" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1155" s="3" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="1156" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1156" s="3" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="1157" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1157" s="3" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="1158" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1158" s="3" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="1159" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1159" s="3" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="1160" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1160" s="3" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="1161" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1161" s="3" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="1162" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1162" s="3" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="1163" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1163" s="3" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="1164" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1164" s="3" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="1165" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1165" s="3" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="1166" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1166" s="3" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="1167" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1167" s="3" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="1168" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1168" s="3" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="1169" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1169" s="3" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="1170" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1170" s="3" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="1171" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1171" s="3" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="1172" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1172" s="3" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="1173" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1173" s="3" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="1174" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1174" s="3" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="1175" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1175" s="3" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1176" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1176" s="3" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="1177" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1177" s="3" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="1178" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1178" s="3" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="1179" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1179" s="3" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="1180" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1180" s="3" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="1181" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1181" s="3" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="1182" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1182" s="3" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="1183" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1183" s="3" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="1184" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1184" s="3" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="1185" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1185" s="3" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="1186" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1186" s="3" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="1187" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1187" s="3" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="1188" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1188" s="3" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="1189" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1189" s="3" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="1190" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1190" s="3" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="1191" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1191" s="3" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="1192" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1192" s="3" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="1193" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1193" s="3" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="1194" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1194" s="3" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="1195" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1195" s="3" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="1196" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1196" s="3" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="1197" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1197" s="3" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="1198" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1198" s="3" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="1199" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1199" s="3" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="1200" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1200" s="3" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="1201" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1201" s="3" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="1202" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1202" s="3" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="1203" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1203" s="3" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="1204" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1204" s="3" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="1205" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1205" s="3" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="1206" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1206" s="3" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="1207" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1207" s="3" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="1208" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1208" s="3" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="1209" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1209" s="3" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="1210" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1210" s="3" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="1211" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1211" s="3" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="1212" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1212" s="3" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="1213" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1213" s="3" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="1214" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1214" s="3" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="1215" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1215" s="3" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="1216" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1216" s="3" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="1217" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1217" s="3" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="1218" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1218" s="3" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="1219" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1219" s="3" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="1220" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1220" s="3" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="1221" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1221" s="3" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="1222" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1222" s="3" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="1223" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1223" s="3" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="1224" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1224" s="3" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="1225" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1225" s="3" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="1226" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1226" s="3" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="1227" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1227" s="3" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="1228" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1228" s="3" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="1229" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1229" s="3" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="1230" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1230" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="1231" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1231" s="3" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="1232" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1232" s="3" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="1233" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1233" s="3" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="1234" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1234" s="3" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="1235" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1235" s="3" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="1236" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1236" s="3" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="1237" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1237" s="3" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="1238" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1238" s="3" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="1239" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1239" s="3" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="1240" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1240" s="3" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="1241" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1241" s="3" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="1242" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1242" s="3" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="1243" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1243" s="3" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="1244" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1244" s="3" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="1245" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1245" s="3" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="1246" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1246" s="3" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="1247" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1247" s="3" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="1248" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1248" s="3" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="1249" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1249" s="3" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="1250" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1250" s="3" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="1251" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1251" s="3" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="1252" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1252" s="3" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="1253" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1253" s="3" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="1254" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1254" s="3" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="1255" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1255" s="3" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="1256" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1256" s="3" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="1257" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1257" s="3" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="1258" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1258" s="3" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="1259" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1259" s="3" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="1260" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1260" s="3" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="1261" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1261" s="3" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="1262" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1262" s="3" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="1263" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1263" s="3" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="1264" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1264" s="3" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="1265" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1265" s="3" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="1266" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1266" s="3" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="1267" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1267" s="3" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="1268" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1268" s="3" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="1269" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1269" s="3" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="1270" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1270" s="3" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="1271" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1271" s="3" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="1272" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1272" s="3" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="1273" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1273" s="3" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="1274" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1274" s="3" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="1275" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1275" s="3" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="1276" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1276" s="3" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="1277" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1277" s="3" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="1278" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1278" s="3" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="1279" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1279" s="3" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="1280" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1280" s="3" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="1281" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1281" s="3" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="1282" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1282" s="3" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="1283" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1283" s="3" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="1284" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1284" s="3" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="1285" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1285" s="3" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="1286" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1286" s="3" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="1287" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1287" s="3" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="1288" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1288" s="3" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="1289" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1289" s="3" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="1290" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1290" s="3" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="1291" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1291" s="3" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="1292" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1292" s="3" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="1293" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1293" s="3" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="1294" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1294" s="3" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="1295" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1295" s="3" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="1296" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1296" s="3" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="1297" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1297" s="3" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="1298" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1298" s="3" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="1299" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1299" s="3" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="1300" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1300" s="3" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="1301" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1301" s="3" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="1302" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1302" s="3" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="1303" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1303" s="3" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="1304" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1304" s="3" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="1305" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1305" s="3" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="1306" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1306" s="3" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="1307" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1307" s="3" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="1308" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1308" s="3" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="1309" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1309" s="3" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="1310" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1310" s="3" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="1311" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1311" s="3" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="1312" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1312" s="3" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="1313" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1313" s="3" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="1314" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1314" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="1315" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1315" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="1316" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1316" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="1317" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1317" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="1318" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1318" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="1319" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1319" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="1320" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1320" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="1321" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1321" s="3" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="1322" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1322" s="3" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="1323" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1323" s="3" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="1324" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1324" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="1325" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1325" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="1326" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1326" s="3" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="1327" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1327" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="1328" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1328" s="3" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="1329" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1329" s="3" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="1330" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1330" s="3" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="1331" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1331" s="3" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="1332" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1332" s="3" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="1333" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1333" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="1334" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1334" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="1335" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1335" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="1336" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1336" s="3" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="1337" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1337" s="3" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="1338" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1338" s="3" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="1339" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1339" s="3" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="1340" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1340" s="3" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="1341" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1341" s="3" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="1342" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1342" s="3" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="1343" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1343" s="3" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="1344" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1344" s="3" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="1345" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1345" s="3" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="1346" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1346" s="3" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="1347" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1347" s="3" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1348" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1348" s="3" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="1349" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1349" s="3" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="1350" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1350" s="3" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="1351" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1351" s="3" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="1352" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1352" s="3" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="1353" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1353" s="3" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="1354" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1354" s="3" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="1355" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1355" s="3" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="1356" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1356" s="3" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="1357" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1357" s="3" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="1358" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1358" s="3" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="1359" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1359" s="3" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="1360" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1360" s="3" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="1361" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1361" s="3" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="1362" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1362" s="3" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="1363" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1363" s="3" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="1364" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1364" s="3" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="1365" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1365" s="3" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="1366" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1366" s="3" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="1367" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1367" s="3" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="1368" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1368" s="3" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="1369" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1369" s="3" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="1370" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1370" s="3" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="1371" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1371" s="3" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="1372" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1372" s="3" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="1373" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1373" s="3" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="1374" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1374" s="3" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="1375" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1375" s="3" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="1376" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1376" s="3" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="1377" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1377" s="3" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="1378" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1378" s="3" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="1379" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1379" s="3" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="1380" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1380" s="3" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="1381" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1381" s="3" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="1382" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1382" s="3" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="1383" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1383" s="3" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="1384" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1384" s="3" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="1385" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1385" s="3" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="1386" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1386" s="3" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="1387" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1387" s="3" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="1388" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1388" s="3" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="1389" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1389" s="3" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="1390" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1390" s="3" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="1391" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1391" s="3" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="1392" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1392" s="3" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="1393" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1393" s="3" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="1394" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1394" s="3" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="1395" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1395" s="3" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1396" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1396" s="3" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="1397" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1397" s="3" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="1398" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1398" s="3" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="1399" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1399" s="3" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="1400" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1400" s="3" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="1401" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1401" s="3" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="1402" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1402" s="3" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="1403" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1403" s="3" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="1404" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1404" s="3" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1405" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1405" s="3" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="1406" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1406" s="3" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="1407" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1407" s="3" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="1408" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1408" s="3" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="1409" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1409" s="3" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="1410" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1410" s="3" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="1411" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1411" s="3" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="1412" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1412" s="3" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="1413" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1413" s="3" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="1414" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1414" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="1415" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1415" s="3" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="1416" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1416" s="3" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="1417" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1417" s="3" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="1418" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1418" s="3" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="1419" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1419" s="3" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="1420" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1420" s="3" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="1421" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1421" s="3" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="1422" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1422" s="3" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="1423" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1423" s="3" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="1424" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1424" s="3" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="1425" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1425" s="3" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="1426" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1426" s="3" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="1427" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1427" s="3" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="1428" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1428" s="3" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="1429" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1429" s="3" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="1430" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1430" s="3" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="1431" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1431" s="3" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="1432" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1432" s="3" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="1433" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1433" s="3" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="1434" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1434" s="3" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="1435" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1435" s="3" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="1436" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1436" s="3" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="1437" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1437" s="3" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="1438" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1438" s="3" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="1439" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1439" s="3" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="1440" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1440" s="3" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="1441" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1441" s="3" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="1442" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1442" s="3" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="1443" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1443" s="3" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="1444" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1444" s="3" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="1445" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1445" s="3" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1446" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1446" s="3" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1447" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1447" s="3" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="1448" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1448" s="3" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="1449" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1449" s="3" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="1450" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1450" s="3" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="1451" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1451" s="3" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="1452" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1452" s="3" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="1453" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1453" s="3" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="1454" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1454" s="3" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="1455" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1455" s="3" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="1456" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1456" s="3" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="1457" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1457" s="3" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="1458" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1458" s="3" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="1459" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1459" s="3" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="1460" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1460" s="3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="1461" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1461" s="3" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="1462" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1462" s="3" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="1463" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1463" s="3" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="1464" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1464" s="3" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="1465" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1465" s="3" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="1466" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1466" s="3" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1467" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1467" s="3" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="1468" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1468" s="3" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="1469" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1469" s="3" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1470" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1470" s="3" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="1471" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1471" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="1472" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1472" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="1473" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1473" s="3" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="1474" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1474" s="3" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="1475" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1475" s="3" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="1476" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1476" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="1477" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1477" s="3" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="1478" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1478" s="3" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="1479" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1479" s="3" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="1480" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1480" s="3" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="1481" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1481" s="3" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="1482" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1482" s="3" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="1483" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1483" s="3" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="1484" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1484" s="3" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="1485" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1485" s="3" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="1486" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1486" s="3" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="1487" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1487" s="3" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="1488" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1488" s="3" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="1489" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1489" s="3" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="1490" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1490" s="3" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="1491" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1491" s="3" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="1492" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1492" s="3" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="1493" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1493" s="3" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="1494" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1494" s="3" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="1495" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1495" s="3" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="1496" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1496" s="3" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="1497" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1497" s="3" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1498" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1498" s="3" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="1499" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1499" s="3" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="1500" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1500" s="3" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="1501" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1501" s="3" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="1502" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1502" s="3" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="1503" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1503" s="3" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="1504" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1504" s="3" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="1505" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1505" s="3" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="1506" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1506" s="3" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="1507" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1507" s="3" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="1508" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1508" s="3" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="1509" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1509" s="3" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="1510" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1510" s="3" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="1511" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1511" s="3" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="1512" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1512" s="3" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="1513" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1513" s="3" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="1514" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1514" s="3" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="1515" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1515" s="3" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="1516" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1516" s="3" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="1517" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1517" s="3" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="1518" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1518" s="3" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="1519" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1519" s="3" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="1520" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1520" s="3" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="1521" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1521" s="3" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="1522" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1522" s="3" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="1523" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1523" s="3" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1524" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1524" s="3" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="1525" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1525" s="3" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="1526" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1526" s="3" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="1527" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1527" s="3" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="1528" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1528" s="3" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="1529" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1529" s="3" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="1530" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1530" s="3" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="1531" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1531" s="3" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="1532" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1532" s="3" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="1533" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1533" s="3" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="1534" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1534" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="1535" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1535" s="3" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="1536" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1536" s="3" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="1537" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1537" s="3" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="1538" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1538" s="3" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="1539" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1539" s="3" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="1540" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1540" s="3" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="1541" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1541" s="3" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="1542" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1542" s="3" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="1543" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1543" s="3" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="1544" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1544" s="3" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="1545" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1545" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="1546" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1546" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="1547" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1547" s="3" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="1548" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1548" s="3" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="1549" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1549" s="3" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="1550" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1550" s="3" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="1551" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1551" s="3" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="1552" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1552" s="3" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="1553" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1553" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="1554" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1554" s="3" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="1555" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1555" s="3" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="1556" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1556" s="3" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="1557" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1557" s="3" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="1558" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1558" s="3" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="1559" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1559" s="3" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="1560" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1560" s="3" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="1561" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1561" s="3" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="1562" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1562" s="3" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="1563" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1563" s="3" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="1564" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1564" s="3" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="1565" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1565" s="3" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="1566" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1566" s="3" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="1567" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1567" s="3" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="1568" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1568" s="3" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="1569" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1569" s="3" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="1570" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1570" s="3" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="1571" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1571" s="3" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="1572" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1572" s="3" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="1573" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1573" s="3" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="1574" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1574" s="3" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="1575" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1575" s="3" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="1576" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1576" s="3" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="1577" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1577" s="3" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="1578" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1578" s="3" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="1579" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1579" s="3" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="1580" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1580" s="3" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="1581" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1581" s="3" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="1582" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1582" s="3" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="1583" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1583" s="3" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="1584" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1584" s="3" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="1585" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1585" s="3" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="1586" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1586" s="3" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="1587" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1587" s="3" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="1588" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1588" s="3" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="1589" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1589" s="3" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="1590" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1590" s="3" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="1591" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1591" s="3" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="1592" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1592" s="3" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="1593" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1593" s="3" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="1594" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1594" s="3" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="1595" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1595" s="3" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="1596" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1596" s="3" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="1597" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1597" s="3" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="1598" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1598" s="3" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="1599" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1599" s="3" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="1600" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1600" s="3" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="1601" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1601" s="3" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="1602" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1602" s="3" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="1603" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1603" s="3" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="1604" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1604" s="3" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="1605" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1605" s="3" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="1606" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1606" s="3" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="1607" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1607" s="3" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="1608" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1608" s="3" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="1609" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1609" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="1610" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1610" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="1611" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1611" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="1612" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1612" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="1613" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1613" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="1614" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1614" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="1615" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1615" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="1616" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1616" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="1617" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1617" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="1618" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1618" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="1619" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1619" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="1620" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1620" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="1621" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1621" s="3"/>
+      <c r="A1621" s="3" t="s">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1622" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1623" t="s">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1624" t="s">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1625" t="s">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1626" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1627" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1628" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1629" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1630" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1631" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1632" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1633" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1634" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1635" t="s">
+        <v>1634</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:A1620"/>

--- a/import_template.xlsx
+++ b/import_template.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A1716"/>
+  <dimension ref="A1:A1715"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
   </cols>
@@ -3072,5922 +3072,5917 @@
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Fai Filtri</v>
+        <v>FAIFILTRI</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>FAIFILTRI</v>
+        <v>FAIRFIELD</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>FAIRFIELD</v>
+        <v>FALCON/MILLENNIUM</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>FALCON/MILLENNIUM</v>
+        <v>FALCONLIFT</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>FALCONLIFT</v>
+        <v>FANTUZZI</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>FANTUZZI</v>
+        <v>FARESIN</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>FARESIN</v>
+        <v>FARESIN-FH</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>FARESIN-FH</v>
+        <v>FARO</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>FARO</v>
+        <v>FAST</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>FAST</v>
+        <v>FAUN</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>FAUN</v>
+        <v>FAW</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>FAW</v>
+        <v>FB-CHAIN</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>FB-CHAIN</v>
+        <v>FBN</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>FBN</v>
+        <v>FDR</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>FDR</v>
+        <v>FEBI</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>FEBI</v>
+        <v>FEELER</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>FEELER</v>
+        <v>FENDT</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>FENDT</v>
+        <v>FENWICK</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>FENWICK</v>
+        <v>FERGAS</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>FERGAS</v>
+        <v>FERRAZ</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>FERRAZ</v>
+        <v>FERRODO</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>FERRODO</v>
+        <v>FERSA</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>FERSA</v>
+        <v>FERVE</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>FERVE</v>
+        <v>FFZ</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>FFZ</v>
+        <v>FIAAM</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>FIAAM</v>
+        <v>FIAT</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>FIAT</v>
+        <v>FIAT HITACHI</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>FIAT HITACHI</v>
+        <v>FIAT KOBELCO</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>FIAT KOBELCO</v>
+        <v>FIAT-ALLIS</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>FIAT-ALLIS</v>
+        <v>FIL-FILTER</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>FIL-FILTER</v>
+        <v>FILTERAFMETING</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>FILTERAFMETING</v>
+        <v>FILTREC</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>FILTREC</v>
+        <v>FILTRON</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>FILTRON</v>
+        <v>FIMAP</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>FIMAP</v>
+        <v>FIORA</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>FIORA</v>
+        <v>FIORELLA</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>FIORELLA</v>
+        <v>FIORENTINI</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>FIORENTINI</v>
+        <v>FISA</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>FISA</v>
+        <v>FLEETGUARD</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>FLEETGUARD</v>
+        <v>FLEXI NARROW AISLE</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>FLEXI NARROW AISLE</v>
+        <v>FLEXON</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>FLEXON</v>
+        <v>FLK</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>FLK</v>
+        <v>FLOJET</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>FLOJET</v>
+        <v>FLOORPUL</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>FLOORPUL</v>
+        <v>FLO-PAC</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>FLO-PAC</v>
+        <v>FMC - AIRPORT</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>FMC - AIRPORT</v>
+        <v>FOLANGSI</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>FOLANGSI</v>
+        <v>FOR</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>FOR</v>
+        <v>FORCE</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>FORCE</v>
+        <v>FORD</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>FORD</v>
+        <v>FORK</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>FORK</v>
+        <v>FORK/ACCESSORIES</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>FORK/ACCESSORIES</v>
+        <v>FORKS</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>FORKS</v>
+        <v>FORKS PIN TYPE</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>FORKS PIN TYPE</v>
+        <v>FOURNIAL</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>FOURNIAL</v>
+        <v>FRAM FILTERS</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>FRAM FILTERS</v>
+        <v>FRANCE HAYON SERVICE</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>FRANCE HAYON SERVICE</v>
+        <v>FRECCIA</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>FRECCIA</v>
+        <v>FREI</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>FREI</v>
+        <v>FREUDENBERG CFW</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>FREUDENBERG CFW</v>
+        <v>FREUDENBERG OLD</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>FREUDENBERG OLD</v>
+        <v>FRIBEL</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>FRIBEL</v>
+        <v>FROETEK</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>FROETEK</v>
+        <v>FST INTEGRAL</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>FST INTEGRAL</v>
+        <v>FTE</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>FTE</v>
+        <v>FTM</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>FTM</v>
+        <v>FTMH</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>FTMH</v>
+        <v>Fuchs</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Fuchs</v>
+        <v>FUCHS OIL</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>FUCHS OIL</v>
+        <v>FUDEX</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>FUDEX</v>
+        <v>FUHR</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>FUHR</v>
+        <v>FUJI ELECTRIC</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>FUJI ELECTRIC</v>
+        <v>FURON</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>FURON</v>
+        <v>FURUKAWA</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>FURUKAWA</v>
+        <v>FUYANG</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>FUYANG</v>
+        <v>G POWER</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>G POWER</v>
+        <v>GALTECH</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>GALTECH</v>
+        <v>GANSOW IPC</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>GANSOW IPC</v>
+        <v>GARPHYTTAN</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>GARPHYTTAN</v>
+        <v>Garrett</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Garrett</v>
+        <v>GASKA</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>GASKA</v>
+        <v>GASVEERUITEINDEN</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>GASVEERUITEINDEN</v>
+        <v>GASVEREN</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>GASVEREN</v>
+        <v>GATES</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>GATES</v>
+        <v>GAYSAN</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>GAYSAN</v>
+        <v>GAZ</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>GAZ</v>
+        <v>GB RICAMBI</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>GB RICAMBI</v>
+        <v>GEHL</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>GEHL</v>
+        <v>GELEIDINGSRING</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>GELEIDINGSRING</v>
+        <v>GENERAL ELECTRIC</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>GENERAL ELECTRIC</v>
+        <v>GENERAL MOTORS</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>GENERAL MOTORS</v>
+        <v>GENGE &amp; THOMA</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>GENGE &amp; THOMA</v>
+        <v>GENIE</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>GENIE</v>
+        <v>GENKINGER</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>GENKINGER</v>
+        <v>GESSMANN</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>GESSMANN</v>
+        <v>GHIBLI</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>GHIBLI</v>
+        <v>GIANT</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>GIANT</v>
+        <v>GIETNUMMER</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>GIETNUMMER</v>
+        <v>GKN</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>GKN</v>
+        <v>GLACIER METAL</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>GLACIER METAL</v>
+        <v>GLAENZER SEURE</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>GLAENZER SEURE</v>
+        <v>GLASER</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>GLASER</v>
+        <v>GLOBALPARTS</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>GLOBALPARTS</v>
+        <v>GLYCO</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>GLYCO</v>
+        <v>GM-IMPCO</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>GM-IMPCO</v>
+        <v>GODREJ</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>GODREJ</v>
+        <v>GOK</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>GOK</v>
+        <v>GOLD VALUE</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>GOLD VALUE</v>
+        <v>GOLDEN BRIGHT</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>GOLDEN BRIGHT</v>
+        <v>GOLDEN FILTER</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>GOLDEN FILTER</v>
+        <v>GOLDHOFER</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>GOLDHOFER</v>
+        <v>GOODSENSE</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>GOODSENSE</v>
+        <v>Goodwill</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Goodwill</v>
+        <v>GOTTWALD</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>GOTTWALD</v>
+        <v>GOULD</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>GOULD</v>
+        <v>GOUPIL</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>GOUPIL</v>
+        <v>G-Part</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>G-Part</v>
+        <v>GPC</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>GPC</v>
+        <v>GRADALL</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>GRADALL</v>
+        <v>GRAMMER</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>GRAMMER</v>
+        <v>GRANIT PARTS</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>GRANIT PARTS</v>
+        <v>GRAZIANO</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>GRAZIANO</v>
+        <v>GRISONI</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>GRISONI</v>
+        <v>GROVE / MANLIFT</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>GROVE / MANLIFT</v>
+        <v>GUARDIAN</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>GUARDIAN</v>
+        <v>GUMASOL</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>GUMASOL</v>
+        <v>GUNCO</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>GUNCO</v>
+        <v>GUNNEBO</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>GUNNEBO</v>
+        <v>HACO</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>HACO</v>
+        <v>Hagglunds</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Hagglunds</v>
+        <v>HAKO</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>HAKO</v>
+        <v>HALDEX</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>HALDEX</v>
+        <v>HALLA</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>HALLA</v>
+        <v>HALLITE</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>HALLITE</v>
+        <v>HAMECH</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>HAMECH</v>
+        <v>HAMLIN</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>HAMLIN</v>
+        <v>HAMM</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>HAMM</v>
+        <v>HANDBAROW</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>HANDBAROW</v>
+        <v>HANGCHA</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>HANGCHA</v>
+        <v>HANIX</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>HANIX</v>
+        <v>HANSELIFTER</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>HANSELIFTER</v>
+        <v>HAO MING</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>HAO MING</v>
+        <v>HAPPICH</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>HAPPICH</v>
+        <v>HARDELLET</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>HARDELLET</v>
+        <v>HARLAN</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>HARLAN</v>
+        <v>HARTING</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>HARTING</v>
+        <v>HARTMANN</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>HARTMANN</v>
+        <v>HASCO</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>HASCO</v>
+        <v>HATZ</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>HATZ</v>
+        <v>HAULOTTE</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>HAULOTTE</v>
+        <v>HAW TUOH</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>HAW TUOH</v>
+        <v>HAYAKAWA ELECTRIC</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>HAYAKAWA ELECTRIC</v>
+        <v>HAYE</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>HAYE</v>
+        <v>HB SWITCH</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>HB SWITCH</v>
+        <v>HC STANG CK45</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>HC STANG CK45</v>
+        <v>HCA</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>HCA</v>
+        <v>HEAT-ON</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>HEAT-ON</v>
+        <v>HEDEN - DANTRUCK</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>HEDEN - DANTRUCK</v>
+        <v>HEJALUX</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>HEJALUX</v>
+        <v>HELI</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>HELI</v>
+        <v>HELLA</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>HELLA</v>
+        <v>HELMAR</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>HELMAR</v>
+        <v>HENGST</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>HENGST</v>
+        <v>HENLEY</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>HENLEY</v>
+        <v>HERCULES HYDRAULIC</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>HERCULES HYDRAULIC</v>
+        <v>HERTH &amp; BUSS</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>HERTH &amp; BUSS</v>
+        <v>HEYD</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>HEYD</v>
+        <v>HF</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>HF</v>
+        <v>HIDROMEK</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>HIDROMEK</v>
+        <v>HIGHLY</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>HIGHLY</v>
+        <v>HINOWA</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>HINOWA</v>
+        <v>HIRSCHMANN</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>HIRSCHMANN</v>
+        <v>HISTOPARTS</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>HISTOPARTS</v>
+        <v>HITACHI</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>HITACHI</v>
+        <v>HITACHI AERIAL PLATFORM</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>HITACHI AERIAL PLATFORM</v>
+        <v>HJS</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>HJS</v>
+        <v>HLG</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>HLG</v>
+        <v>HOBBS</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v>HOBBS</v>
+        <v>HOIST</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>HOIST</v>
+        <v>HOISTMAXX</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>HOISTMAXX</v>
+        <v>HOLLAND LIFT</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>HOLLAND LIFT</v>
+        <v>HONDA</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>HONDA</v>
+        <v>HONEYWELL</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="str">
-        <v>HONEYWELL</v>
+        <v>HOOGERDIJK</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v>HOOGERDIJK</v>
+        <v>HOUCHIN</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v>HOUCHIN</v>
+        <v>HOVESIN</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v>HOVESIN</v>
+        <v>HP HIDRAULICA</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>HP HIDRAULICA</v>
+        <v>HPI</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v>HPI</v>
+        <v>HUACHENG</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="str">
-        <v>HUACHENG</v>
+        <v>HUACHENG - TAIXING</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v>HUACHENG - TAIXING</v>
+        <v>HUAXIN</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="str">
-        <v>HUAXIN</v>
+        <v>HUBTEX</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v>HUBTEX</v>
+        <v>HU-LIFT</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="str">
-        <v>HU-LIFT</v>
+        <v>HURTH</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v>HURTH</v>
+        <v>HYDAC</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v>HYDAC</v>
+        <v>HYDRAFORCE</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>HYDRAFORCE</v>
+        <v>HYDRAPP</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v>HYDRAPP</v>
+        <v>HYDRECO</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v>HYDRECO</v>
+        <v>HYDROFLEX</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="str">
-        <v>HYDROFLEX</v>
+        <v>HYDRO-MECA</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>HYDRO-MECA</v>
+        <v>HYDROPARTS</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>HYDROPARTS</v>
+        <v>HYDRO-TEK</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v>HYDRO-TEK</v>
+        <v>HYSTER</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>HYSTER</v>
+        <v>HYTSU</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>HYTSU</v>
+        <v>HYUNDAI</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="str">
-        <v>HYUNDAI</v>
+        <v>ICEM</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="str">
-        <v>ICEM</v>
+        <v>ICHIMENS</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="str">
-        <v>ICHIMENS</v>
+        <v>IES</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="str">
-        <v>IES</v>
+        <v>IFAK SYSTEM</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="str">
-        <v>IFAK SYSTEM</v>
+        <v>IFM</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>IFM</v>
+        <v>IGUS</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>IGUS</v>
+        <v>IHC</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="str">
-        <v>IHC</v>
+        <v>IHI</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="str">
-        <v>IHI</v>
+        <v>IHI AERIAL PLATFORM</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="str">
-        <v>IHI AERIAL PLATFORM</v>
+        <v>IKO</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="str">
-        <v>IKO</v>
+        <v>IKRON</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="str">
-        <v>IKRON</v>
+        <v>IMASEN</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="str">
-        <v>IMASEN</v>
+        <v>IMAXX</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="str">
-        <v>IMAXX</v>
+        <v>IMER</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="str">
-        <v>IMER</v>
+        <v>IMPORTCHAIN</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="str">
-        <v>IMPORTCHAIN</v>
+        <v>INA</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="str">
-        <v>INA</v>
+        <v>INDAK</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="str">
-        <v>INDAK</v>
+        <v>INDOS</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="str">
-        <v>INDOS</v>
+        <v>INDUSTRIESERVICEJUNG</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="str">
-        <v>INDUSTRIESERVICEJUNG</v>
+        <v>INGERSOLL-RAND</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="str">
-        <v>INGERSOLL-RAND</v>
+        <v>INT HARVESTER</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="str">
-        <v>INT HARVESTER</v>
+        <v>INTELLA</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="str">
-        <v>INTELLA</v>
+        <v>INTERLIFT</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="str">
-        <v>INTERLIFT</v>
+        <v>INTERNAL PART NUMBER</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="str">
-        <v>INTERNAL PART NUMBER</v>
+        <v>INTERNATIONAL</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="str">
-        <v>INTERNATIONAL</v>
+        <v>INTERNATIONAL RECTIF</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="str">
-        <v>INTERNATIONAL RECTIF</v>
+        <v>INTERNORMEN</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="str">
-        <v>INTERNORMEN</v>
+        <v>INTERPIECES</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="str">
-        <v>INTERPIECES</v>
+        <v>INTRUPA</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="str">
-        <v>INTRUPA</v>
+        <v>INVICTA FORKS</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="str">
-        <v>INVICTA FORKS</v>
+        <v>IPC - JOYSTICKS</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="str">
-        <v>IPC - JOYSTICKS</v>
+        <v>IPS</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="str">
-        <v>IPS</v>
+        <v>IRION</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="str">
-        <v>IRION</v>
+        <v>IS</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="str">
-        <v>IS</v>
+        <v>ISAL</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="str">
-        <v>ISAL</v>
+        <v>ISEKI</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="str">
-        <v>ISEKI</v>
+        <v>ISJUNG</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="str">
-        <v>ISJUNG</v>
+        <v>ISKRA</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="str">
-        <v>ISKRA</v>
+        <v>ISRINGHAUSEN</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>ISRINGHAUSEN</v>
+        <v>ISUZU</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="str">
-        <v>ISUZU</v>
+        <v>ITALCAB</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="str">
-        <v>ITALCAB</v>
+        <v>ITALCARRELLI</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="str">
-        <v>ITALCARRELLI</v>
+        <v>ITALMACCHINE</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="str">
-        <v>ITALMACCHINE</v>
+        <v>ITT/CANNON</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="str">
-        <v>ITT/CANNON</v>
+        <v>ITW SWITCHES</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="str">
-        <v>ITW SWITCHES</v>
+        <v>IVECO</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="str">
-        <v>IVECO</v>
+        <v>IXYS</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="str">
-        <v>IXYS</v>
+        <v>JAC</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="str">
-        <v>JAC</v>
+        <v>JAGTENBERG</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="str">
-        <v>JAGTENBERG</v>
+        <v>JAMSONS</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="str">
-        <v>JAMSONS</v>
+        <v>JAZGOT</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="str">
-        <v>JAZGOT</v>
+        <v>JBT</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="str">
-        <v>JBT</v>
+        <v>JCB</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="str">
-        <v>JCB</v>
+        <v>JCC</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="str">
-        <v>JCC</v>
+        <v>JEHYCO</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="str">
-        <v>JEHYCO</v>
+        <v>JELAU</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="str">
-        <v>JELAU</v>
+        <v>JGL</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="str">
-        <v>JGL</v>
+        <v>JHECO</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="str">
-        <v>JHECO</v>
+        <v>JIDECO</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="str">
-        <v>JIDECO</v>
+        <v>JIMRAY</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="str">
-        <v>JIMRAY</v>
+        <v>JINHUA WINNER</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="str">
-        <v>JINHUA WINNER</v>
+        <v>JINWEI</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="str">
-        <v>JINWEI</v>
+        <v>JLG</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="str">
-        <v>JLG</v>
+        <v>JOHN DEERE</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="str">
-        <v>JOHN DEERE</v>
+        <v>JP</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="str">
-        <v>JP</v>
+        <v>JR MERRITT</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="str">
-        <v>JR MERRITT</v>
+        <v>JUCAR</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="str">
-        <v>JUCAR</v>
+        <v>JULI</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="str">
-        <v>JULI</v>
+        <v>JUMBO</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="str">
-        <v>JUMBO</v>
+        <v>JUNGHEINRICH</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="str">
-        <v>JUNGHEINRICH</v>
+        <v>JURA FILTRATION</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="str">
-        <v>JURA FILTRATION</v>
+        <v>KAB</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="str">
-        <v>KAB</v>
+        <v>KABEL</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="str">
-        <v>KABEL</v>
+        <v>KABELSCHLEPP</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="str">
-        <v>KABELSCHLEPP</v>
+        <v>Kaishan</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="str">
-        <v>Kaishan</v>
+        <v>KALMAR</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="str">
-        <v>KALMAR</v>
+        <v>KALORI</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="str">
-        <v>KALORI</v>
+        <v>Kamaz</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="str">
-        <v>Kamaz</v>
+        <v>KANGDA</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="str">
-        <v>KANGDA</v>
+        <v>KARAKUS</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="str">
-        <v>KARAKUS</v>
+        <v>KARL G KLINGA</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="str">
-        <v>KARL G KLINGA</v>
+        <v>KAT</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="str">
-        <v>KAT</v>
+        <v>KAUP</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="str">
-        <v>KAUP</v>
+        <v>KAWASAKI</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="str">
-        <v>KAWASAKI</v>
+        <v>KAYABA-INDUSTRY</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="str">
-        <v>KAYABA-INDUSTRY</v>
+        <v>KAYER</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="str">
-        <v>KAYER</v>
+        <v>KEB</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="str">
-        <v>KEB</v>
+        <v>KEBA</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="str">
-        <v>KEBA</v>
+        <v>KEMTEX</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="str">
-        <v>KEMTEX</v>
+        <v>KENTRUCK-ROBUR</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="str">
-        <v>KENTRUCK-ROBUR</v>
+        <v>KESSLER</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="str">
-        <v>KESSLER</v>
+        <v>KETA HYDRAULICS</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="str">
-        <v>KETA HYDRAULICS</v>
+        <v>KETTINGPIN TYPE 2</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="str">
-        <v>KETTINGPIN TYPE 2</v>
+        <v>KETTINGTREKKER</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="str">
-        <v>KETTINGTREKKER</v>
+        <v>KFT</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="str">
-        <v>KFT</v>
+        <v>KILOUTOU</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="str">
-        <v>KILOUTOU</v>
+        <v>KINGLIFTER TERBERG</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="str">
-        <v>KINGLIFTER TERBERG</v>
+        <v>KINGSTATE</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="str">
-        <v>KINGSTATE</v>
+        <v>KISER</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="str">
-        <v>KISER</v>
+        <v>KISSLING</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="str">
-        <v>KISSLING</v>
+        <v>KITAHARA</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="str">
-        <v>KITAHARA</v>
+        <v>KLADIVAR</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="str">
-        <v>KLADIVAR</v>
+        <v>KLAUKE</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="str">
-        <v>KLAUKE</v>
+        <v>KLAXON</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="str">
-        <v>KLAXON</v>
+        <v>KLIMAT SYSTEM</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="str">
-        <v>KLIMAT SYSTEM</v>
+        <v>KNECHT</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="str">
-        <v>KNECHT</v>
+        <v>KNORR</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="str">
-        <v>KNORR</v>
+        <v>KNOTT</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="str">
-        <v>KNOTT</v>
+        <v>KOBELCO</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="str">
-        <v>KOBELCO</v>
+        <v>KOHLER</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="str">
-        <v>KOHLER</v>
+        <v>KOJO</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="str">
-        <v>KOJO</v>
+        <v>KOK</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="str">
-        <v>KOK</v>
+        <v>KOKUSAN DENKI</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="str">
-        <v>KOKUSAN DENKI</v>
+        <v>KOLBENSCHMIDT</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="str">
-        <v>KOLBENSCHMIDT</v>
+        <v>KOMATSU</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="str">
-        <v>KOMATSU</v>
+        <v>KOMATSU TELESCOPIC HANDLERS</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="str">
-        <v>KOMATSU TELESCOPIC HANDLERS</v>
+        <v>KONECRANES</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="str">
-        <v>KONECRANES</v>
+        <v>KOOI-AAP</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="str">
-        <v>KOOI-AAP</v>
+        <v>KOOL/CHARBON</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="str">
-        <v>KOOL/CHARBON</v>
+        <v>KOOLKITS</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="str">
-        <v>KOOLKITS</v>
+        <v>KORDEL</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="str">
-        <v>KORDEL</v>
+        <v>KOSTAL</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="str">
-        <v>KOSTAL</v>
+        <v>KOYO</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="str">
-        <v>KOYO</v>
+        <v>KP JOINTS</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="str">
-        <v>KP JOINTS</v>
+        <v>KPC</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="str">
-        <v>KPC</v>
+        <v>Kraft</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="str">
-        <v>Kraft</v>
+        <v>Kraftmann</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="str">
-        <v>Kraftmann</v>
+        <v>KRAMER ALLRAD</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="str">
-        <v>KRAMER ALLRAD</v>
+        <v>KRAMP</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="str">
-        <v>KRAMP</v>
+        <v>KRAUF</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="str">
-        <v>KRAUF</v>
+        <v>KRAUS</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="str">
-        <v>KRAUS</v>
+        <v>KRONEN</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="str">
-        <v>KRONEN</v>
+        <v>KRUGER VERLADETECHN.</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="str">
-        <v>KRUGER VERLADETECHN.</v>
+        <v>KTR</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="str">
-        <v>KTR</v>
+        <v>KTS</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="str">
-        <v>KTS</v>
+        <v>KUBLER</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="str">
-        <v>KUBLER</v>
+        <v>KUBOTA</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="str">
-        <v>KUBOTA</v>
+        <v>KYORITSU KEIKI</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="str">
-        <v>KYORITSU KEIKI</v>
+        <v>KYOSAN-DENKI</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="str">
-        <v>KYOSAN-DENKI</v>
+        <v>KÄRCHER</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="str">
-        <v>KÄRCHER</v>
+        <v>L3 SERVICE PRO</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="str">
-        <v>L3 SERVICE PRO</v>
+        <v>Lada</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="str">
-        <v>Lada</v>
+        <v>LADEBORDWANDTECHNIK</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="str">
-        <v>LADEBORDWANDTECHNIK</v>
+        <v>LAFIS</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="str">
-        <v>LAFIS</v>
+        <v>LAG</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="str">
-        <v>LAG</v>
+        <v>LAMBORGHINI TRACTORS</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="str">
-        <v>LAMBORGHINI TRACTORS</v>
+        <v>LAMPEN</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="str">
-        <v>LAMPEN</v>
+        <v>LANCER</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="str">
-        <v>LANCER</v>
+        <v>LANCER BOSS</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="str">
-        <v>LANCER BOSS</v>
+        <v>LANDI PATTON</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="str">
-        <v>LANDI PATTON</v>
+        <v>LANDINI</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="str">
-        <v>LANDINI</v>
+        <v>LANSING</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="str">
-        <v>LANSING</v>
+        <v>LAP</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="str">
-        <v>LAP</v>
+        <v>LAPP</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="str">
-        <v>LAPP</v>
+        <v>LATEC</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="str">
-        <v>LATEC</v>
+        <v>LAVOR</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="str">
-        <v>LAVOR</v>
+        <v>LEB</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="str">
-        <v>LEB</v>
+        <v>LEBEN</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="str">
-        <v>LEBEN</v>
+        <v>Lecar</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="str">
-        <v>Lecar</v>
+        <v>LEGRAND</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="str">
-        <v>LEGRAND</v>
+        <v>LEIJENAAR</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="str">
-        <v>LEIJENAAR</v>
+        <v>LEMKEN</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="str">
-        <v>LEMKEN</v>
+        <v>LENZE</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="str">
-        <v>LENZE</v>
+        <v>LEROY SOMER</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="str">
-        <v>LEROY SOMER</v>
+        <v>LESTER</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="str">
-        <v>LESTER</v>
+        <v>LESTER ELECTRICAL</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="str">
-        <v>LESTER ELECTRICAL</v>
+        <v>LETRIKA</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="str">
-        <v>LETRIKA</v>
+        <v>LEYLAND</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="str">
-        <v>LEYLAND</v>
+        <v>LGCE</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="str">
-        <v>LGCE</v>
+        <v>LGCE (SDLG)</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="str">
-        <v>LGCE (SDLG)</v>
+        <v>LGMG</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="str">
-        <v>LGMG</v>
+        <v>LIANCHENG</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="str">
-        <v>LIANCHENG</v>
+        <v>LIBE</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="str">
-        <v>LIBE</v>
+        <v>LIEBHERR</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="str">
-        <v>LIEBHERR</v>
+        <v>LIFT RITE</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="str">
-        <v>LIFT RITE</v>
+        <v>LIFTLUX</v>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="str">
-        <v>LIFTLUX</v>
+        <v>LIFTPART</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="str">
-        <v>LIFTPART</v>
+        <v>LIFT-TEK ELECAR</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="str">
-        <v>LIFT-TEK ELECAR</v>
+        <v>Lifttruc</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="str">
-        <v>Lifttruc</v>
+        <v>LINAK</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="str">
-        <v>LINAK</v>
+        <v>LINCOLN</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="str">
-        <v>LINCOLN</v>
+        <v>LINDE</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="str">
-        <v>LINDE</v>
+        <v>LINEMASTER</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="str">
-        <v>LINEMASTER</v>
+        <v>LINSEN PARTS</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="str">
-        <v>LINSEN PARTS</v>
+        <v>LINTEC</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="str">
-        <v>LINTEC</v>
+        <v>LITTELFUSE</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="str">
-        <v>LITTELFUSE</v>
+        <v>LITTLE GIANT</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="str">
-        <v>LITTLE GIANT</v>
+        <v>LITTLE MULE</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="str">
-        <v>LITTLE MULE</v>
+        <v>LIUGONG</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="str">
-        <v>LIUGONG</v>
+        <v>Livni</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="str">
-        <v>Livni</v>
+        <v>LM</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="str">
-        <v>LM</v>
+        <v>LMV</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="str">
-        <v>LMV</v>
+        <v>LOC</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="str">
-        <v>LOC</v>
+        <v>LOCTITE</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="str">
-        <v>LOCTITE</v>
+        <v>Locust</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="str">
-        <v>Locust</v>
+        <v>LOGITRANS</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="str">
-        <v>LOGITRANS</v>
+        <v>LOMBARDINI</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="str">
-        <v>LOMBARDINI</v>
+        <v>Lonking</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="str">
-        <v>Lonking</v>
+        <v>LONKING FORKLIFT</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="str">
-        <v>LONKING FORKLIFT</v>
+        <v>LOVATO</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="str">
-        <v>LOVATO</v>
+        <v>LOVATO ELECTRIC</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="str">
-        <v>LOVATO ELECTRIC</v>
+        <v>Lovol</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="str">
-        <v>Lovol</v>
+        <v>LPG</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="str">
-        <v>LPG</v>
+        <v>LPM</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="str">
-        <v>LPM</v>
+        <v>LPS</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="str">
-        <v>LPS</v>
+        <v>LTE</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="str">
-        <v>LTE</v>
+        <v>LUBERFINER</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="str">
-        <v>LUBERFINER</v>
+        <v>LUCAS</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="str">
-        <v>LUCAS</v>
+        <v>LUCIDITY</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="str">
-        <v>LUCIDITY</v>
+        <v>LUDA</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="str">
-        <v>LUDA</v>
+        <v>LUGLI</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="str">
-        <v>LUGLI</v>
+        <v>LUK KOPPELINGEN</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="str">
-        <v>LUK KOPPELINGEN</v>
+        <v>LUMIACTION</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="str">
-        <v>LUMIACTION</v>
+        <v>M.A.N.</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="str">
-        <v>M.A.N.</v>
+        <v>M.G. JUDD</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="str">
-        <v>M.G. JUDD</v>
+        <v>M+S HYDRAULIC</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="str">
-        <v>M+S HYDRAULIC</v>
+        <v>MAFELEC</v>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="str">
-        <v>MAFELEC</v>
+        <v>MAFI</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="str">
-        <v>MAFI</v>
+        <v>MAGAZINER</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="str">
-        <v>MAGAZINER</v>
+        <v>MAGMIRROR</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="str">
-        <v>MAGMIRROR</v>
+        <v>MAGNETI MARELLI</v>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="str">
-        <v>MAGNETI MARELLI</v>
+        <v>MAGNET-SCHULTZ</v>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="str">
-        <v>MAGNET-SCHULTZ</v>
+        <v>MAGNI</v>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="str">
-        <v>MAGNI</v>
+        <v>MAHLE</v>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="str">
-        <v>MAHLE</v>
+        <v>MALLORY</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="str">
-        <v>MALLORY</v>
+        <v>MAN</v>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="str">
-        <v>MAN</v>
+        <v>MANDIGERS</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="str">
-        <v>MANDIGERS</v>
+        <v>MANDO</v>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="str">
-        <v>MANDO</v>
+        <v>MANILEC</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="str">
-        <v>MANILEC</v>
+        <v>MANITOU</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="str">
-        <v>MANITOU</v>
+        <v>MANN &amp; HUMMEL</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="str">
-        <v>MANN &amp; HUMMEL</v>
+        <v>MANN-FILTER</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="str">
-        <v>MANN-FILTER</v>
+        <v>MARIBA</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="str">
-        <v>MARIBA</v>
+        <v>MARIOTTI</v>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="str">
-        <v>MARIOTTI</v>
+        <v>MARKLIFT</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="str">
-        <v>MARKLIFT</v>
+        <v>MAROO MCS</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="str">
-        <v>MAROO MCS</v>
+        <v>MARQUARDT</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="str">
-        <v>MARQUARDT</v>
+        <v>MASSEY FERGUSON</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="str">
-        <v>MASSEY FERGUSON</v>
+        <v>MAST</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="str">
-        <v>MAST</v>
+        <v>MASTROL AFMETING</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="str">
-        <v>MASTROL AFMETING</v>
+        <v>MATBRO</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="str">
-        <v>MATBRO</v>
+        <v>MATCH FILTER</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="str">
-        <v>MATCH FILTER</v>
+        <v>MATRIX</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="str">
-        <v>MATRIX</v>
+        <v>MATSUSHITA</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="str">
-        <v>MATSUSHITA</v>
+        <v>MAVCIOGLU</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="str">
-        <v>MAVCIOGLU</v>
+        <v>MAXIFORCE</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="str">
-        <v>MAXIFORCE</v>
+        <v>MAXIGRIP</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="str">
-        <v>MAXIGRIP</v>
+        <v>MAXIMAL</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="str">
-        <v>MAXIMAL</v>
+        <v>MAXION</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="str">
-        <v>MAXION</v>
+        <v>MAZ</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="str">
-        <v>MAZ</v>
+        <v>MAZDA</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="str">
-        <v>MAZDA</v>
+        <v>MAZON</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="str">
-        <v>MAZON</v>
+        <v>MB TRAC</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="str">
-        <v>MB TRAC</v>
+        <v>MBB-PALFINGER</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="str">
-        <v>MBB-PALFINGER</v>
+        <v>MBO</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="str">
-        <v>MBO</v>
+        <v>MC CORMICK</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="str">
-        <v>MC CORMICK</v>
+        <v>MC GILL</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="str">
-        <v>MC GILL</v>
+        <v>MCB-ELEKTRISCH</v>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="str">
-        <v>MCB-ELEKTRISCH</v>
+        <v>MCC</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="str">
-        <v>MCC</v>
+        <v>McConnel</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="str">
-        <v>McConnel</v>
+        <v>MEAT &amp; DORIA</v>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="str">
-        <v>MEAT &amp; DORIA</v>
+        <v>MEC</v>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="str">
-        <v>MEC</v>
+        <v>MECALAC</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="str">
-        <v>MECALAC</v>
+        <v>MECATRACTION</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="str">
-        <v>MECATRACTION</v>
+        <v>MEFRO</v>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="str">
-        <v>MEFRO</v>
+        <v>MEGA CARBON</v>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="str">
-        <v>MEGA CARBON</v>
+        <v>MEGA PARTS</v>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="str">
-        <v>MEGA PARTS</v>
+        <v>MEIDEN</v>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="str">
-        <v>MEIDEN</v>
+        <v>MEINENG</v>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="str">
-        <v>MEINENG</v>
+        <v>MELCO</v>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="str">
-        <v>MELCO</v>
+        <v>MENKE</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="str">
-        <v>MENKE</v>
+        <v>MERCEDES</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="str">
-        <v>MERCEDES</v>
+        <v>MERIT</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="str">
-        <v>MERIT</v>
+        <v>MERITOR</v>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="str">
-        <v>MERITOR</v>
+        <v>MERLO</v>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="str">
-        <v>MERLO</v>
+        <v>METALROTA</v>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="str">
-        <v>METALROTA</v>
+        <v>METARIS</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="str">
-        <v>METARIS</v>
+        <v>METELLI</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="str">
-        <v>METELLI</v>
+        <v>METER</v>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="str">
-        <v>METER</v>
+        <v>Metso</v>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="str">
-        <v>Metso</v>
+        <v>MEYER</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="str">
-        <v>MEYER</v>
+        <v>MF</v>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="str">
-        <v>MF</v>
+        <v>MFC</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="str">
-        <v>MFC</v>
+        <v>MGW</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="str">
-        <v>MGW</v>
+        <v>MIAG</v>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="str">
-        <v>MIAG</v>
+        <v>MIC SA</v>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="str">
-        <v>MIC SA</v>
+        <v>MICHIGAN SEAT</v>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="str">
-        <v>MICHIGAN SEAT</v>
+        <v>MICO</v>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="str">
-        <v>MICO</v>
+        <v>MICRO SWITCH</v>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="str">
-        <v>MICRO SWITCH</v>
+        <v>MICROPOWER</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="str">
-        <v>MICROPOWER</v>
+        <v>MIDAC</v>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="str">
-        <v>MIDAC</v>
+        <v>MIDORI</v>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="str">
-        <v>MIDORI</v>
+        <v>MIKUNI</v>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="str">
-        <v>MIKUNI</v>
+        <v>MILSCO</v>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="str">
-        <v>MILSCO</v>
+        <v>MINEX</v>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="str">
-        <v>MINEX</v>
+        <v>MINIPRESS</v>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="str">
-        <v>MINIPRESS</v>
+        <v>MINTOR</v>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="str">
-        <v>MINTOR</v>
+        <v>MINUTEMAN SWEEPER</v>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="str">
-        <v>MINUTEMAN SWEEPER</v>
+        <v>Miraglio</v>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="str">
-        <v>Miraglio</v>
+        <v>MIRALBUENO</v>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="str">
-        <v>MIRALBUENO</v>
+        <v>MISELLI</v>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="str">
-        <v>MISELLI</v>
+        <v>MITSUBISHI</v>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="str">
-        <v>MITSUBISHI</v>
+        <v>MITSUBOSHI</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="str">
-        <v>MITSUBOSHI</v>
+        <v>MIUNSKE</v>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="str">
-        <v>MIUNSKE</v>
+        <v>MLPD</v>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="str">
-        <v>MLPD</v>
+        <v>MOBILE PALLET TRUCK</v>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="str">
-        <v>MOBILE PALLET TRUCK</v>
+        <v>MOFFETT</v>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="str">
-        <v>MOFFETT</v>
+        <v>MOL</v>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="str">
-        <v>MOL</v>
+        <v>MOLEX</v>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="str">
-        <v>MOLEX</v>
+        <v>MONARK DIESEL</v>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="str">
-        <v>MONARK DIESEL</v>
+        <v>MONROE</v>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="str">
-        <v>MONROE</v>
+        <v>Montabert</v>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="str">
-        <v>Montabert</v>
+        <v>MONTINI</v>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="str">
-        <v>MONTINI</v>
+        <v>MORA</v>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="str">
-        <v>MORA</v>
+        <v>MORRISON</v>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="str">
-        <v>MORRISON</v>
+        <v>MOTEC</v>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="str">
-        <v>MOTEC</v>
+        <v>MOTORAD</v>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="str">
-        <v>MOTORAD</v>
+        <v>MOULD-ON RUBBER WHL.</v>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="str">
-        <v>MOULD-ON RUBBER WHL.</v>
+        <v>MOVEXX</v>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="str">
-        <v>MOVEXX</v>
+        <v>MOVIMOTOR</v>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="str">
-        <v>MOVIMOTOR</v>
+        <v>MP FILTRI</v>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="str">
-        <v>MP FILTRI</v>
+        <v>MTA</v>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="str">
-        <v>MTA</v>
+        <v>MTK</v>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="str">
-        <v>MTK</v>
+        <v>MTT</v>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="str">
-        <v>MTT</v>
+        <v>MTZ</v>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="str">
-        <v>MTZ</v>
+        <v>MULAG</v>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="str">
-        <v>MULAG</v>
+        <v>MULTIONE</v>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="str">
-        <v>MULTIONE</v>
+        <v>MULTIQUIP</v>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="str">
-        <v>MULTIQUIP</v>
+        <v>MULTITEL</v>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="str">
-        <v>MULTITEL</v>
+        <v>MULTITON</v>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="str">
-        <v>MULTITON</v>
+        <v>MUSTANG</v>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="str">
-        <v>MUSTANG</v>
+        <v>MVP</v>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="str">
-        <v>MVP</v>
+        <v>MWM</v>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="str">
-        <v>MWM</v>
+        <v>NACCO</v>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="str">
-        <v>NACCO</v>
+        <v>NACHI</v>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="str">
-        <v>NACHI</v>
+        <v>NADELLA</v>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="str">
-        <v>NADELLA</v>
+        <v>NAGARES</v>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="str">
-        <v>NAGARES</v>
+        <v>NANCHIN</v>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="str">
-        <v>NANCHIN</v>
+        <v>NAPA</v>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="str">
-        <v>NAPA</v>
+        <v>NAPCO</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="str">
-        <v>NAPCO</v>
+        <v>NARVA</v>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="str">
-        <v>NARVA</v>
+        <v>NATIONAL</v>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="str">
-        <v>NATIONAL</v>
+        <v>NAVISTAR</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="str">
-        <v>NAVISTAR</v>
+        <v>NB PARTS</v>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="str">
-        <v>NB PARTS</v>
+        <v>NBR</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="str">
-        <v>NBR</v>
+        <v>NDC</v>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="str">
-        <v>NDC</v>
+        <v>Nefaz</v>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="str">
-        <v>Nefaz</v>
+        <v>NESAN</v>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="str">
-        <v>NESAN</v>
+        <v>NETMOTOR</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="str">
-        <v>NETMOTOR</v>
+        <v>NEUSON</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="str">
-        <v>NEUSON</v>
+        <v>NEW DEP BEARING</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="str">
-        <v>NEW DEP BEARING</v>
+        <v>NEW HOLLAND</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="str">
-        <v>NEW HOLLAND</v>
+        <v>NEXEN</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="str">
-        <v>NEXEN</v>
+        <v>NGK</v>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="str">
-        <v>NGK</v>
+        <v>NHC-NEW REF.</v>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="str">
-        <v>NHC-NEW REF.</v>
+        <v>NICERA</v>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="str">
-        <v>NICERA</v>
+        <v>NICHIYU</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="str">
-        <v>NICHIYU</v>
+        <v>NIDEC</v>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="str">
-        <v>NIDEC</v>
+        <v>NIELSEN HOLST</v>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="str">
-        <v>NIELSEN HOLST</v>
+        <v>NIFTYLIFT</v>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="str">
-        <v>NIFTYLIFT</v>
+        <v>NIKKI</v>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="str">
-        <v>NIKKI</v>
+        <v>NIKKO</v>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="str">
-        <v>NIKKO</v>
+        <v>NILES</v>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="str">
-        <v>NILES</v>
+        <v>NILFISK</v>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="str">
-        <v>NILFISK</v>
+        <v>NILOS</v>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="str">
-        <v>NILOS</v>
+        <v>NINGBO EH-FORKS</v>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="str">
-        <v>NINGBO EH-FORKS</v>
+        <v>NINGBO HAIAN</v>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="str">
-        <v>NINGBO HAIAN</v>
+        <v>NIPPON PARTS</v>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="str">
-        <v>NIPPON PARTS</v>
+        <v>NIPPON-DENSO</v>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="str">
-        <v>NIPPON-DENSO</v>
+        <v>NISSAN</v>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="str">
-        <v>NISSAN</v>
+        <v>NKB</v>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="str">
-        <v>NKB</v>
+        <v>NMC-WOLLARD</v>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="str">
-        <v>NMC-WOLLARD</v>
+        <v>NOBLELIFT</v>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="str">
-        <v>NOBLELIFT</v>
+        <v>NOELL</v>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="str">
-        <v>NOELL</v>
+        <v>NOK</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="str">
-        <v>NOK</v>
+        <v>Nord Yada</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="str">
-        <v>Nord Yada</v>
+        <v>NORDIC</v>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="str">
-        <v>NORDIC</v>
+        <v>NORDJOK-BRUSSEL</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="str">
-        <v>NORDJOK-BRUSSEL</v>
+        <v>NORMA LAMP</v>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="str">
-        <v>NORMA LAMP</v>
+        <v>NORMA-HAR</v>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="str">
-        <v>NORMA-HAR</v>
+        <v>NORTHMAN</v>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="str">
-        <v>NORTHMAN</v>
+        <v>NOVELTEK</v>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="str">
-        <v>NOVELTEK</v>
+        <v>NSK ROTA</v>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="str">
-        <v>NSK ROTA</v>
+        <v>NSK-HOOVER</v>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="str">
-        <v>NSK-HOOVER</v>
+        <v>NSN-NATO</v>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="str">
-        <v>NSN-NATO</v>
+        <v>NTN</v>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="str">
-        <v>NTN</v>
+        <v>NU-LIFT</v>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="str">
-        <v>NU-LIFT</v>
+        <v>NUMATIC</v>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="str">
-        <v>NUMATIC</v>
+        <v>NUOVA DETAS</v>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="str">
-        <v>NUOVA DETAS</v>
+        <v>NUOVA ELLETRA</v>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="str">
-        <v>NUOVA ELLETRA</v>
+        <v>NZTA</v>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="str">
-        <v>NZTA</v>
+        <v>O&amp;K</v>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="str">
-        <v>O&amp;K</v>
+        <v>O(MEGA)ET</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="str">
-        <v>O(MEGA)ET</v>
+        <v>OEB</v>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="str">
-        <v>OEB</v>
+        <v>OEM</v>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="str">
-        <v>OEM</v>
+        <v>OEM CONTROLS</v>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="str">
-        <v>OEM CONTROLS</v>
+        <v>OGNIBENE</v>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="str">
-        <v>OGNIBENE</v>
+        <v>OGNIBENE ELETTROMECCANICA</v>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="str">
-        <v>OGNIBENE ELETTROMECCANICA</v>
+        <v>OHIO MOTOR</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="str">
-        <v>OHIO MOTOR</v>
+        <v>OIL SEAL</v>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="str">
-        <v>OIL SEAL</v>
+        <v>OIL SISTEM</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="str">
-        <v>OIL SISTEM</v>
+        <v>OLD TRACPIECES</v>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="str">
-        <v>OLD TRACPIECES</v>
+        <v>OLDCARS</v>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="str">
-        <v>OLDCARS</v>
+        <v>OLDHAM</v>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="str">
-        <v>OLDHAM</v>
+        <v>OLEOSTAR</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="str">
-        <v>OLEOSTAR</v>
+        <v>OLIEK M STOFLIP</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="str">
-        <v>OLIEK M STOFLIP</v>
+        <v>OMCI</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="str">
-        <v>OMCI</v>
+        <v>OMG</v>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="str">
-        <v>OMG</v>
+        <v>OMM</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="str">
-        <v>OMM</v>
+        <v>OMMELIFT</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="str">
-        <v>OMMELIFT</v>
+        <v>OMP</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="str">
-        <v>OMP</v>
+        <v>OM-PIMESPO</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="str">
-        <v>OM-PIMESPO</v>
+        <v>OMRON</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="str">
-        <v>OMRON</v>
+        <v>OPEL</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="str">
-        <v>OPEL</v>
+        <v>Opkon</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="str">
-        <v>Opkon</v>
+        <v>OPTIBELT</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="str">
-        <v>OPTIBELT</v>
+        <v>ORGATOP</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="str">
-        <v>ORGATOP</v>
+        <v>O-RING AFMETING</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="str">
-        <v>O-RING AFMETING</v>
+        <v>ORMIC</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="str">
-        <v>ORMIC</v>
+        <v>OSRAM</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="str">
-        <v>OSRAM</v>
+        <v>OTEHALL</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="str">
-        <v>OTEHALL</v>
+        <v>OTTAWA</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="str">
-        <v>OTTAWA</v>
+        <v>OUD MERK BEPCO</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="str">
-        <v>OUD MERK BEPCO</v>
+        <v>OUD MERK TRACPIECES</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="str">
-        <v>OUD MERK TRACPIECES</v>
+        <v>OUHAI</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="str">
-        <v>OUHAI</v>
+        <v>OYMAK</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="str">
-        <v>OYMAK</v>
+        <v>OZGUR</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="str">
-        <v>OZGUR</v>
+        <v>PACAUTO</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="str">
-        <v>PACAUTO</v>
+        <v>PAI</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="str">
-        <v>PAI</v>
+        <v>PAIGE PLUS</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="str">
-        <v>PAIGE PLUS</v>
+        <v>PALFINGER</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="str">
-        <v>PALFINGER</v>
+        <v>PALL</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="str">
-        <v>PALL</v>
+        <v>PANCLEAN</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="str">
-        <v>PANCLEAN</v>
+        <v>PAPST</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="str">
-        <v>PAPST</v>
+        <v>PARIS-RHONE</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="str">
-        <v>PARIS-RHONE</v>
+        <v>PARKER</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="str">
-        <v>PARKER</v>
+        <v>PARTSLIFT</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="str">
-        <v>PARTSLIFT</v>
+        <v>PASTIL BAKVORM</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="str">
-        <v>PASTIL BAKVORM</v>
+        <v>PASTIL GEBOGEN</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="str">
-        <v>PASTIL GEBOGEN</v>
+        <v>PATRIA</v>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="str">
-        <v>PATRIA</v>
+        <v>PAYEN</v>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="str">
-        <v>PAYEN</v>
+        <v>PAYMOVER</v>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="str">
-        <v>PAYMOVER</v>
+        <v>PAZ</v>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="str">
-        <v>PAZ</v>
+        <v>PB</v>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="str">
-        <v>PB</v>
+        <v>PBM</v>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="str">
-        <v>PBM</v>
+        <v>PCMIDWEST</v>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="str">
-        <v>PCMIDWEST</v>
+        <v>PDF</v>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="str">
-        <v>PDF</v>
+        <v>PEFRA</v>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="str">
-        <v>PEFRA</v>
+        <v>PEG - FENWICK</v>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="str">
-        <v>PEG - FENWICK</v>
+        <v>PEGASO</v>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="str">
-        <v>PEGASO</v>
+        <v>PELJOB</v>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="str">
-        <v>PELJOB</v>
+        <v>PENNY &amp; GILES</v>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="str">
-        <v>PENNY &amp; GILES</v>
+        <v>PEPPERL+FUCHS</v>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="str">
-        <v>PEPPERL+FUCHS</v>
+        <v>PEREI</v>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="str">
-        <v>PEREI</v>
+        <v>PERFILTER</v>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="str">
-        <v>PERFILTER</v>
+        <v>PERKINS</v>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="str">
-        <v>PERKINS</v>
+        <v>PERROT</v>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="str">
-        <v>PERROT</v>
+        <v>PETTIBONE</v>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="str">
-        <v>PETTIBONE</v>
+        <v>PEUGEOT</v>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="str">
-        <v>PEUGEOT</v>
+        <v>PFAFF</v>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="str">
-        <v>PFAFF</v>
+        <v>PG DRIVES TECHNOLOGY</v>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="str">
-        <v>PG DRIVES TECHNOLOGY</v>
+        <v>PHILADELPHIA</v>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="str">
-        <v>PHILADELPHIA</v>
+        <v>PHILIPS</v>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="str">
-        <v>PHILIPS</v>
+        <v>Phoenix</v>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="str">
-        <v>Phoenix</v>
+        <v>PHOENIX CONTACT</v>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="str">
-        <v>PHOENIX CONTACT</v>
+        <v>PIERALISI</v>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="str">
-        <v>PIERALISI</v>
+        <v>PIERBURG</v>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="str">
-        <v>PIERBURG</v>
+        <v>PILOT</v>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="str">
-        <v>PILOT</v>
+        <v>PIM</v>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="str">
-        <v>PIM</v>
+        <v>PISTONSAN</v>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="str">
-        <v>PISTONSAN</v>
+        <v>PITTMAN</v>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="str">
-        <v>PITTMAN</v>
+        <v>PIZZATO</v>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="str">
-        <v>PIZZATO</v>
+        <v>PLASTIME</v>
       </c>
     </row>
     <row r="1212">
       <c r="A1212" t="str">
-        <v>PLASTIME</v>
+        <v>PNEUMATIC TYRE</v>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" t="str">
-        <v>PNEUMATIC TYRE</v>
+        <v>PNEUTRON</v>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="str">
-        <v>PNEUTRON</v>
+        <v>POLLAK</v>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="str">
-        <v>POLLAK</v>
+        <v>POLYPAC</v>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" t="str">
-        <v>POLYPAC</v>
+        <v>POTTER &amp; BRUMFIELD</v>
       </c>
     </row>
     <row r="1217">
       <c r="A1217" t="str">
-        <v>POTTER &amp; BRUMFIELD</v>
+        <v>POWERBOSS</v>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" t="str">
-        <v>POWERBOSS</v>
+        <v>POWERCONN</v>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="str">
-        <v>POWERCONN</v>
+        <v>POWERSEAL</v>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="str">
-        <v>POWERSEAL</v>
+        <v>PPM</v>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="str">
-        <v>PPM</v>
+        <v>PQ CONTROLS</v>
       </c>
     </row>
     <row r="1222">
       <c r="A1222" t="str">
-        <v>PQ CONTROLS</v>
+        <v>PRAMAC</v>
       </c>
     </row>
     <row r="1223">
       <c r="A1223" t="str">
-        <v>PRAMAC</v>
+        <v>PRAT</v>
       </c>
     </row>
     <row r="1224">
       <c r="A1224" t="str">
-        <v>PRAT</v>
+        <v>Prc</v>
       </c>
     </row>
     <row r="1225">
       <c r="A1225" t="str">
-        <v>Prc</v>
+        <v>PRECO</v>
       </c>
     </row>
     <row r="1226">
       <c r="A1226" t="str">
-        <v>PRECO</v>
+        <v>PRESSOL</v>
       </c>
     </row>
     <row r="1227">
       <c r="A1227" t="str">
-        <v>PRESSOL</v>
+        <v>PRESS-ON TYRE</v>
       </c>
     </row>
     <row r="1228">
       <c r="A1228" t="str">
-        <v>PRESS-ON TYRE</v>
+        <v>PRESTOLITE</v>
       </c>
     </row>
     <row r="1229">
       <c r="A1229" t="str">
-        <v>PRESTOLITE</v>
+        <v>PRILLINGER</v>
       </c>
     </row>
     <row r="1230">
       <c r="A1230" t="str">
-        <v>PRILLINGER</v>
+        <v>PRIME MOVER</v>
       </c>
     </row>
     <row r="1231">
       <c r="A1231" t="str">
-        <v>PRIME MOVER</v>
+        <v>PRINS</v>
       </c>
     </row>
     <row r="1232">
       <c r="A1232" t="str">
-        <v>PRINS</v>
+        <v>PROCONECT</v>
       </c>
     </row>
     <row r="1233">
       <c r="A1233" t="str">
-        <v>PROCONECT</v>
+        <v>PRONAR</v>
       </c>
     </row>
     <row r="1234">
       <c r="A1234" t="str">
-        <v>PRONAR</v>
+        <v>PROPLAST</v>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="str">
-        <v>PROPLAST</v>
+        <v>PROTECH</v>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="str">
-        <v>PROTECH</v>
+        <v>PROTO</v>
       </c>
     </row>
     <row r="1237">
       <c r="A1237" t="str">
-        <v>PROTO</v>
+        <v>PSH</v>
       </c>
     </row>
     <row r="1238">
       <c r="A1238" t="str">
-        <v>PSH</v>
+        <v>PSV WIPER LTD</v>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" t="str">
-        <v>PSV WIPER LTD</v>
+        <v>PTP</v>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="str">
-        <v>PTP</v>
+        <v>PUBLISHING</v>
       </c>
     </row>
     <row r="1241">
       <c r="A1241" t="str">
-        <v>PUBLISHING</v>
+        <v>PUDENZ</v>
       </c>
     </row>
     <row r="1242">
       <c r="A1242" t="str">
-        <v>PUDENZ</v>
+        <v>PURFLUX</v>
       </c>
     </row>
     <row r="1243">
       <c r="A1243" t="str">
-        <v>PURFLUX</v>
+        <v>PUROLATOR</v>
       </c>
     </row>
     <row r="1244">
       <c r="A1244" t="str">
-        <v>PUROLATOR</v>
+        <v>QFS</v>
       </c>
     </row>
     <row r="1245">
       <c r="A1245" t="str">
-        <v>QFS</v>
+        <v>QQE TECHNOLOGY C</v>
       </c>
     </row>
     <row r="1246">
       <c r="A1246" t="str">
-        <v>QQE TECHNOLOGY C</v>
+        <v>Q-TRONIC</v>
       </c>
     </row>
     <row r="1247">
       <c r="A1247" t="str">
-        <v>Q-TRONIC</v>
+        <v>QUZHOU</v>
       </c>
     </row>
     <row r="1248">
       <c r="A1248" t="str">
-        <v>QUZHOU</v>
+        <v>R&amp;R LPG</v>
       </c>
     </row>
     <row r="1249">
       <c r="A1249" t="str">
-        <v>R&amp;R LPG</v>
+        <v>R.A.S.E.D.</v>
       </c>
     </row>
     <row r="1250">
       <c r="A1250" t="str">
-        <v>R.A.S.E.D.</v>
+        <v>RAAL</v>
       </c>
     </row>
     <row r="1251">
       <c r="A1251" t="str">
-        <v>RAAL</v>
+        <v>RABO LIGHT</v>
       </c>
     </row>
     <row r="1252">
       <c r="A1252" t="str">
-        <v>RABO LIGHT</v>
+        <v>RACOR</v>
       </c>
     </row>
     <row r="1253">
       <c r="A1253" t="str">
-        <v>RACOR</v>
+        <v>RADER VOGEL</v>
       </c>
     </row>
     <row r="1254">
       <c r="A1254" t="str">
-        <v>RADER VOGEL</v>
+        <v>RAFI</v>
       </c>
     </row>
     <row r="1255">
       <c r="A1255" t="str">
-        <v>RAFI</v>
+        <v>RAJYSAN</v>
       </c>
     </row>
     <row r="1256">
       <c r="A1256" t="str">
-        <v>RAJYSAN</v>
+        <v>RAM MOUNTS</v>
       </c>
     </row>
     <row r="1257">
       <c r="A1257" t="str">
-        <v>RAM MOUNTS</v>
+        <v>RANGER</v>
       </c>
     </row>
     <row r="1258">
       <c r="A1258" t="str">
-        <v>RANGER</v>
+        <v>RAPID LIFT</v>
       </c>
     </row>
     <row r="1259">
       <c r="A1259" t="str">
-        <v>RAPID LIFT</v>
+        <v>RAPID PARTS ADAPTALI</v>
       </c>
     </row>
     <row r="1260">
       <c r="A1260" t="str">
-        <v>RAPID PARTS ADAPTALI</v>
+        <v>RATCLIFF</v>
       </c>
     </row>
     <row r="1261">
       <c r="A1261" t="str">
-        <v>RATCLIFF</v>
+        <v>RAVAS</v>
       </c>
     </row>
     <row r="1262">
       <c r="A1262" t="str">
-        <v>RAVAS</v>
+        <v>RAVIOLI</v>
       </c>
     </row>
     <row r="1263">
       <c r="A1263" t="str">
-        <v>RAVIOLI</v>
+        <v>RAYMOND</v>
       </c>
     </row>
     <row r="1264">
       <c r="A1264" t="str">
-        <v>RAYMOND</v>
+        <v>RayTalk</v>
       </c>
     </row>
     <row r="1265">
       <c r="A1265" t="str">
-        <v>RayTalk</v>
+        <v>R-B COMPONENTES</v>
       </c>
     </row>
     <row r="1266">
       <c r="A1266" t="str">
-        <v>R-B COMPONENTES</v>
+        <v>RCM</v>
       </c>
     </row>
     <row r="1267">
       <c r="A1267" t="str">
-        <v>RCM</v>
+        <v>REALS</v>
       </c>
     </row>
     <row r="1268">
       <c r="A1268" t="str">
-        <v>REALS</v>
+        <v>RECHNER</v>
       </c>
     </row>
     <row r="1269">
       <c r="A1269" t="str">
-        <v>RECHNER</v>
+        <v>RELIANCE</v>
       </c>
     </row>
     <row r="1270">
       <c r="A1270" t="str">
-        <v>RELIANCE</v>
+        <v>REMA</v>
       </c>
     </row>
     <row r="1271">
       <c r="A1271" t="str">
-        <v>REMA</v>
+        <v>REMKA FLEX</v>
       </c>
     </row>
     <row r="1272">
       <c r="A1272" t="str">
-        <v>REMKA FLEX</v>
+        <v>RENAULT</v>
       </c>
     </row>
     <row r="1273">
       <c r="A1273" t="str">
-        <v>RENAULT</v>
+        <v>RENOLD PLC</v>
       </c>
     </row>
     <row r="1274">
       <c r="A1274" t="str">
-        <v>RENOLD PLC</v>
+        <v>REXNORD</v>
       </c>
     </row>
     <row r="1275">
       <c r="A1275" t="str">
-        <v>REXNORD</v>
+        <v>REXROTH</v>
       </c>
     </row>
     <row r="1276">
       <c r="A1276" t="str">
-        <v>REXROTH</v>
+        <v>RGR</v>
       </c>
     </row>
     <row r="1277">
       <c r="A1277" t="str">
-        <v>RGR</v>
+        <v>RHEINTACHO</v>
       </c>
     </row>
     <row r="1278">
       <c r="A1278" t="str">
-        <v>RHEINTACHO</v>
+        <v>RIKEN</v>
       </c>
     </row>
     <row r="1279">
       <c r="A1279" t="str">
-        <v>RIKEN</v>
+        <v>RING</v>
       </c>
     </row>
     <row r="1280">
       <c r="A1280" t="str">
-        <v>RING</v>
+        <v>RIVETKETTINGPIN</v>
       </c>
     </row>
     <row r="1281">
       <c r="A1281" t="str">
-        <v>RIVETKETTINGPIN</v>
+        <v>RIXIN</v>
       </c>
     </row>
     <row r="1282">
       <c r="A1282" t="str">
-        <v>RIXIN</v>
+        <v>RMF</v>
       </c>
     </row>
     <row r="1283">
       <c r="A1283" t="str">
-        <v>RMF</v>
+        <v>RMH</v>
       </c>
     </row>
     <row r="1284">
       <c r="A1284" t="str">
-        <v>RMH</v>
+        <v>ROAD</v>
       </c>
     </row>
     <row r="1285">
       <c r="A1285" t="str">
-        <v>ROAD</v>
+        <v>ROCKINGER</v>
       </c>
     </row>
     <row r="1286">
       <c r="A1286" t="str">
-        <v>ROCKINGER</v>
+        <v>ROCLA</v>
       </c>
     </row>
     <row r="1287">
       <c r="A1287" t="str">
-        <v>ROCLA</v>
+        <v>ROFAN</v>
       </c>
     </row>
     <row r="1288">
       <c r="A1288" t="str">
-        <v>ROFAN</v>
+        <v>RONCARI</v>
       </c>
     </row>
     <row r="1289">
       <c r="A1289" t="str">
-        <v>RONCARI</v>
+        <v>ROOTS</v>
       </c>
     </row>
     <row r="1290">
       <c r="A1290" t="str">
-        <v>ROOTS</v>
+        <v>ROQUET</v>
       </c>
     </row>
     <row r="1291">
       <c r="A1291" t="str">
-        <v>ROQUET</v>
+        <v>ROS</v>
       </c>
     </row>
     <row r="1292">
       <c r="A1292" t="str">
-        <v>ROS</v>
+        <v>Rossvik</v>
       </c>
     </row>
     <row r="1293">
       <c r="A1293" t="str">
-        <v>Rossvik</v>
+        <v>Rostar</v>
       </c>
     </row>
     <row r="1294">
       <c r="A1294" t="str">
-        <v>Rostar</v>
+        <v>ROTAFIL</v>
       </c>
     </row>
     <row r="1295">
       <c r="A1295" t="str">
-        <v>ROTAFIL</v>
+        <v>ROWAN</v>
       </c>
     </row>
     <row r="1296">
       <c r="A1296" t="str">
-        <v>ROWAN</v>
+        <v>RUBBER TRACK</v>
       </c>
     </row>
     <row r="1297">
       <c r="A1297" t="str">
-        <v>RUBBER TRACK</v>
+        <v>RUBENPOWER</v>
       </c>
     </row>
     <row r="1298">
       <c r="A1298" t="str">
-        <v>RUBENPOWER</v>
+        <v>RUIGUANG LIGHTING</v>
       </c>
     </row>
     <row r="1299">
       <c r="A1299" t="str">
-        <v>RUIGUANG LIGHTING</v>
+        <v>RUILI</v>
       </c>
     </row>
     <row r="1300">
       <c r="A1300" t="str">
-        <v>RUILI</v>
+        <v>RUNMAX</v>
       </c>
     </row>
     <row r="1301">
       <c r="A1301" t="str">
-        <v>RUNMAX</v>
+        <v>RYCO</v>
       </c>
     </row>
     <row r="1302">
       <c r="A1302" t="str">
-        <v>RYCO</v>
+        <v>SABELT</v>
       </c>
     </row>
     <row r="1303">
       <c r="A1303" t="str">
-        <v>SABELT</v>
+        <v>SACHS</v>
       </c>
     </row>
     <row r="1304">
       <c r="A1304" t="str">
-        <v>SACHS</v>
+        <v>SAFE-T-ALERT</v>
       </c>
     </row>
     <row r="1305">
       <c r="A1305" t="str">
-        <v>SAFE-T-ALERT</v>
+        <v>SAFETY JOGGER</v>
       </c>
     </row>
     <row r="1306">
       <c r="A1306" t="str">
-        <v>SAFETY JOGGER</v>
+        <v>SAFETYSHOP</v>
       </c>
     </row>
     <row r="1307">
       <c r="A1307" t="str">
-        <v>SAFETYSHOP</v>
+        <v>SAFHOLLAND</v>
       </c>
     </row>
     <row r="1308">
       <c r="A1308" t="str">
-        <v>SAFHOLLAND</v>
+        <v>SAFIM</v>
       </c>
     </row>
     <row r="1309">
       <c r="A1309" t="str">
-        <v>SAFIM</v>
+        <v>SAGE</v>
       </c>
     </row>
     <row r="1310">
       <c r="A1310" t="str">
-        <v>SAGE</v>
+        <v>SAIA</v>
       </c>
     </row>
     <row r="1311">
       <c r="A1311" t="str">
-        <v>SAIA</v>
+        <v>SAKAE</v>
       </c>
     </row>
     <row r="1312">
       <c r="A1312" t="str">
-        <v>SAKAE</v>
+        <v>SAKAGAMI</v>
       </c>
     </row>
     <row r="1313">
       <c r="A1313" t="str">
-        <v>SAKAGAMI</v>
+        <v>SAKURA</v>
       </c>
     </row>
     <row r="1314">
       <c r="A1314" t="str">
-        <v>SAKURA</v>
+        <v>SALEV</v>
       </c>
     </row>
     <row r="1315">
       <c r="A1315" t="str">
-        <v>SALEV</v>
+        <v>SAMAG</v>
       </c>
     </row>
     <row r="1316">
       <c r="A1316" t="str">
-        <v>SAMAG</v>
+        <v>SAMBRON</v>
       </c>
     </row>
     <row r="1317">
       <c r="A1317" t="str">
-        <v>SAMBRON</v>
+        <v>SAME</v>
       </c>
     </row>
     <row r="1318">
       <c r="A1318" t="str">
-        <v>SAME</v>
+        <v>SAMMOON</v>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" t="str">
-        <v>SAMMOON</v>
+        <v>Sampa</v>
       </c>
     </row>
     <row r="1320">
       <c r="A1320" t="str">
-        <v>Sampa</v>
+        <v>SAMSUNG</v>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" t="str">
-        <v>SAMSUNG</v>
+        <v>SAMUK</v>
       </c>
     </row>
     <row r="1322">
       <c r="A1322" t="str">
-        <v>SAMUK</v>
+        <v>SANDEN</v>
       </c>
     </row>
     <row r="1323">
       <c r="A1323" t="str">
-        <v>SANDEN</v>
+        <v>SANDERSON</v>
       </c>
     </row>
     <row r="1324">
       <c r="A1324" t="str">
-        <v>SANDERSON</v>
+        <v>Sandvik</v>
       </c>
     </row>
     <row r="1325">
       <c r="A1325" t="str">
-        <v>Sandvik</v>
+        <v>SANGONG</v>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="str">
-        <v>SANGONG</v>
+        <v>Sania</v>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="str">
-        <v>Sania</v>
+        <v>SANKEI</v>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="str">
-        <v>SANKEI</v>
+        <v>SANY</v>
       </c>
     </row>
     <row r="1329">
       <c r="A1329" t="str">
-        <v>SANY</v>
+        <v>SANYO DENKI</v>
       </c>
     </row>
     <row r="1330">
       <c r="A1330" t="str">
-        <v>SANYO DENKI</v>
+        <v>SARRAZIN</v>
       </c>
     </row>
     <row r="1331">
       <c r="A1331" t="str">
-        <v>SARRAZIN</v>
+        <v>SATMO-RECORD</v>
       </c>
     </row>
     <row r="1332">
       <c r="A1332" t="str">
-        <v>SATMO-RECORD</v>
+        <v>SAUER DANFOSS</v>
       </c>
     </row>
     <row r="1333">
       <c r="A1333" t="str">
-        <v>SAUER DANFOSS</v>
+        <v>SAVECO</v>
       </c>
     </row>
     <row r="1334">
       <c r="A1334" t="str">
-        <v>SAVECO</v>
+        <v>SAWTRAK</v>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" t="str">
-        <v>SAWTRAK</v>
+        <v>SAXBY</v>
       </c>
     </row>
     <row r="1336">
       <c r="A1336" t="str">
-        <v>SAXBY</v>
+        <v>SCANIA</v>
       </c>
     </row>
     <row r="1337">
       <c r="A1337" t="str">
-        <v>SCANIA</v>
+        <v>SCARAB</v>
       </c>
     </row>
     <row r="1338">
       <c r="A1338" t="str">
-        <v>SCARAB</v>
+        <v>SCHABMULLER</v>
       </c>
     </row>
     <row r="1339">
       <c r="A1339" t="str">
-        <v>SCHABMULLER</v>
+        <v>SCHAEFF</v>
       </c>
     </row>
     <row r="1340">
       <c r="A1340" t="str">
-        <v>SCHAEFF</v>
+        <v>SCHAFFELHUBER</v>
       </c>
     </row>
     <row r="1341">
       <c r="A1341" t="str">
-        <v>SCHAFFELHUBER</v>
+        <v>SCHALTBAU</v>
       </c>
     </row>
     <row r="1342">
       <c r="A1342" t="str">
-        <v>SCHALTBAU</v>
+        <v>SCHIEFER</v>
       </c>
     </row>
     <row r="1343">
       <c r="A1343" t="str">
-        <v>SCHIEFER</v>
+        <v>SCHILTZ</v>
       </c>
     </row>
     <row r="1344">
       <c r="A1344" t="str">
-        <v>SCHILTZ</v>
+        <v>SCHLEGEL</v>
       </c>
     </row>
     <row r="1345">
       <c r="A1345" t="str">
-        <v>SCHLEGEL</v>
+        <v>SCHMERSAL</v>
       </c>
     </row>
     <row r="1346">
       <c r="A1346" t="str">
-        <v>SCHMERSAL</v>
+        <v>SCHNEEKETTEN</v>
       </c>
     </row>
     <row r="1347">
       <c r="A1347" t="str">
-        <v>SCHNEEKETTEN</v>
+        <v>SCHNEIDER</v>
       </c>
     </row>
     <row r="1348">
       <c r="A1348" t="str">
-        <v>SCHNEIDER</v>
+        <v>Schneider Electric</v>
       </c>
     </row>
     <row r="1349">
       <c r="A1349" t="str">
-        <v>Schneider Electric</v>
+        <v>SCHONBUCH</v>
       </c>
     </row>
     <row r="1350">
       <c r="A1350" t="str">
-        <v>SCHONBUCH</v>
+        <v>SCHRACK</v>
       </c>
     </row>
     <row r="1351">
       <c r="A1351" t="str">
-        <v>SCHRACK</v>
+        <v>SCHUPP</v>
       </c>
     </row>
     <row r="1352">
       <c r="A1352" t="str">
-        <v>SCHUPP</v>
+        <v>SCHÄFFER</v>
       </c>
     </row>
     <row r="1353">
       <c r="A1353" t="str">
-        <v>SCHÄFFER</v>
+        <v>SCOMA</v>
       </c>
     </row>
     <row r="1354">
       <c r="A1354" t="str">
-        <v>SCOMA</v>
+        <v>SDF PARTS</v>
       </c>
     </row>
     <row r="1355">
       <c r="A1355" t="str">
-        <v>SDF PARTS</v>
+        <v>SDH</v>
       </c>
     </row>
     <row r="1356">
       <c r="A1356" t="str">
-        <v>SDH</v>
+        <v>SDLG</v>
       </c>
     </row>
     <row r="1357">
       <c r="A1357" t="str">
-        <v>SDLG</v>
+        <v>SEALS</v>
       </c>
     </row>
     <row r="1358">
       <c r="A1358" t="str">
-        <v>SEALS</v>
+        <v>SEARS</v>
       </c>
     </row>
     <row r="1359">
       <c r="A1359" t="str">
-        <v>SEARS</v>
+        <v>SEAT (ZETELS)</v>
       </c>
     </row>
     <row r="1360">
       <c r="A1360" t="str">
-        <v>SEAT (ZETELS)</v>
+        <v>SEAT INDUSTRIES</v>
       </c>
     </row>
     <row r="1361">
       <c r="A1361" t="str">
-        <v>SEAT INDUSTRIES</v>
+        <v>SECURON</v>
       </c>
     </row>
     <row r="1362">
       <c r="A1362" t="str">
-        <v>SECURON</v>
+        <v>SEDIS</v>
       </c>
     </row>
     <row r="1363">
       <c r="A1363" t="str">
-        <v>SEDIS</v>
+        <v>SEEGERRINGEN</v>
       </c>
     </row>
     <row r="1364">
       <c r="A1364" t="str">
-        <v>SEEGERRINGEN</v>
+        <v>SEM</v>
       </c>
     </row>
     <row r="1365">
       <c r="A1365" t="str">
-        <v>SEM</v>
+        <v>SEMAX</v>
       </c>
     </row>
     <row r="1366">
       <c r="A1366" t="str">
-        <v>SEMAX</v>
+        <v>SEMIKRON</v>
       </c>
     </row>
     <row r="1367">
       <c r="A1367" t="str">
-        <v>SEMIKRON</v>
+        <v>SENNEBOGEN</v>
       </c>
     </row>
     <row r="1368">
       <c r="A1368" t="str">
-        <v>SENNEBOGEN</v>
+        <v>Separ</v>
       </c>
     </row>
     <row r="1369">
       <c r="A1369" t="str">
-        <v>Separ</v>
+        <v>SEVCON</v>
       </c>
     </row>
     <row r="1370">
       <c r="A1370" t="str">
-        <v>SEVCON</v>
+        <v>SHANGLI</v>
       </c>
     </row>
     <row r="1371">
       <c r="A1371" t="str">
-        <v>SHANGLI</v>
+        <v>SHANMON</v>
       </c>
     </row>
     <row r="1372">
       <c r="A1372" t="str">
-        <v>SHANMON</v>
+        <v>Shantui</v>
       </c>
     </row>
     <row r="1373">
       <c r="A1373" t="str">
-        <v>Shantui</v>
+        <v>SHENG TENG</v>
       </c>
     </row>
     <row r="1374">
       <c r="A1374" t="str">
-        <v>SHENG TENG</v>
+        <v>SHIMADZU</v>
       </c>
     </row>
     <row r="1375">
       <c r="A1375" t="str">
-        <v>SHIMADZU</v>
+        <v>SHIN CHIN</v>
       </c>
     </row>
     <row r="1376">
       <c r="A1376" t="str">
-        <v>SHIN CHIN</v>
+        <v>SHINKO</v>
       </c>
     </row>
     <row r="1377">
       <c r="A1377" t="str">
-        <v>SHINKO</v>
+        <v>SIBA</v>
       </c>
     </row>
     <row r="1378">
       <c r="A1378" t="str">
-        <v>SIBA</v>
+        <v>SIBICAR</v>
       </c>
     </row>
     <row r="1379">
       <c r="A1379" t="str">
-        <v>SIBICAR</v>
+        <v>SIBTEK</v>
       </c>
     </row>
     <row r="1380">
       <c r="A1380" t="str">
-        <v>SIBTEK</v>
+        <v>SICHELSCHMIDT</v>
       </c>
     </row>
     <row r="1381">
       <c r="A1381" t="str">
-        <v>SICHELSCHMIDT</v>
+        <v>SICK</v>
       </c>
     </row>
     <row r="1382">
       <c r="A1382" t="str">
-        <v>SICK</v>
+        <v>SIDEM</v>
       </c>
     </row>
     <row r="1383">
       <c r="A1383" t="str">
-        <v>SIDEM</v>
+        <v>SIEMENS</v>
       </c>
     </row>
     <row r="1384">
       <c r="A1384" t="str">
-        <v>SIEMENS</v>
+        <v>SIGNET SYSTEMS</v>
       </c>
     </row>
     <row r="1385">
       <c r="A1385" t="str">
-        <v>SIGNET SYSTEMS</v>
+        <v>SILVERSTONE</v>
       </c>
     </row>
     <row r="1386">
       <c r="A1386" t="str">
-        <v>SILVERSTONE</v>
+        <v>SIMAI</v>
       </c>
     </row>
     <row r="1387">
       <c r="A1387" t="str">
-        <v>SIMAI</v>
+        <v>SIMMS</v>
       </c>
     </row>
     <row r="1388">
       <c r="A1388" t="str">
-        <v>SIMMS</v>
+        <v>SIMON</v>
       </c>
     </row>
     <row r="1389">
       <c r="A1389" t="str">
-        <v>SIMON</v>
+        <v>Simpeco</v>
       </c>
     </row>
     <row r="1390">
       <c r="A1390" t="str">
-        <v>Simpeco</v>
+        <v>SIN JIN</v>
       </c>
     </row>
     <row r="1391">
       <c r="A1391" t="str">
-        <v>SIN JIN</v>
+        <v>SINCANLI</v>
       </c>
     </row>
     <row r="1392">
       <c r="A1392" t="str">
-        <v>SINCANLI</v>
+        <v>SING YUNG</v>
       </c>
     </row>
     <row r="1393">
       <c r="A1393" t="str">
-        <v>SING YUNG</v>
+        <v>SINOBOOM</v>
       </c>
     </row>
     <row r="1394">
       <c r="A1394" t="str">
-        <v>SINOBOOM</v>
+        <v>Sinomach</v>
       </c>
     </row>
     <row r="1395">
       <c r="A1395" t="str">
-        <v>Sinomach</v>
+        <v>SIR</v>
       </c>
     </row>
     <row r="1396">
       <c r="A1396" t="str">
-        <v>SIR</v>
+        <v>SIRENA</v>
       </c>
     </row>
     <row r="1397">
       <c r="A1397" t="str">
-        <v>SIRENA</v>
+        <v>SIROCCO</v>
       </c>
     </row>
     <row r="1398">
       <c r="A1398" t="str">
-        <v>SIROCCO</v>
+        <v>SIROCO</v>
       </c>
     </row>
     <row r="1399">
       <c r="A1399" t="str">
-        <v>SIROCO</v>
+        <v>SISU</v>
       </c>
     </row>
     <row r="1400">
       <c r="A1400" t="str">
-        <v>SISU</v>
+        <v>SITRAK</v>
       </c>
     </row>
     <row r="1401">
       <c r="A1401" t="str">
-        <v>SITRAK</v>
+        <v>SKF</v>
       </c>
     </row>
     <row r="1402">
       <c r="A1402" t="str">
-        <v>SKF</v>
+        <v>SKU BEPCO QUALITY</v>
       </c>
     </row>
     <row r="1403">
       <c r="A1403" t="str">
-        <v>SKU BEPCO QUALITY</v>
+        <v>SKY TRAK</v>
       </c>
     </row>
     <row r="1404">
       <c r="A1404" t="str">
-        <v>SKY TRAK</v>
+        <v>SKYJACK</v>
       </c>
     </row>
     <row r="1405">
       <c r="A1405" t="str">
-        <v>SKYJACK</v>
+        <v>SLEUTELNUMMER</v>
       </c>
     </row>
     <row r="1406">
       <c r="A1406" t="str">
-        <v>SLEUTELNUMMER</v>
+        <v>SLOTNUMMER</v>
       </c>
     </row>
     <row r="1407">
       <c r="A1407" t="str">
-        <v>SLOTNUMMER</v>
+        <v>SLP</v>
       </c>
     </row>
     <row r="1408">
       <c r="A1408" t="str">
-        <v>SLP</v>
+        <v>SMAT NORD</v>
       </c>
     </row>
     <row r="1409">
       <c r="A1409" t="str">
-        <v>SMAT NORD</v>
+        <v>SME ELETTRONICA</v>
       </c>
     </row>
     <row r="1410">
       <c r="A1410" t="str">
-        <v>SME ELETTRONICA</v>
+        <v>SMH</v>
       </c>
     </row>
     <row r="1411">
       <c r="A1411" t="str">
-        <v>SMH</v>
+        <v>SMH REPRESENTATION</v>
       </c>
     </row>
     <row r="1412">
       <c r="A1412" t="str">
-        <v>SMH REPRESENTATION</v>
+        <v>SMITHS MOTOR</v>
       </c>
     </row>
     <row r="1413">
       <c r="A1413" t="str">
-        <v>SMITHS MOTOR</v>
+        <v>SNEEUWKETTING KONIG</v>
       </c>
     </row>
     <row r="1414">
       <c r="A1414" t="str">
-        <v>SNEEUWKETTING KONIG</v>
+        <v>SNF</v>
       </c>
     </row>
     <row r="1415">
       <c r="A1415" t="str">
-        <v>SNF</v>
+        <v>SNORKEL</v>
       </c>
     </row>
     <row r="1416">
       <c r="A1416" t="str">
-        <v>SNORKEL</v>
+        <v>SNP</v>
       </c>
     </row>
     <row r="1417">
       <c r="A1417" t="str">
-        <v>SNP</v>
+        <v>SNR</v>
       </c>
     </row>
     <row r="1418">
       <c r="A1418" t="str">
-        <v>SNR</v>
+        <v>SOBELTOP</v>
       </c>
     </row>
     <row r="1419">
       <c r="A1419" t="str">
-        <v>SOBELTOP</v>
+        <v>SOCAGE</v>
       </c>
     </row>
     <row r="1420">
       <c r="A1420" t="str">
-        <v>SOCAGE</v>
+        <v>SOEPELE LASKABEL</v>
       </c>
     </row>
     <row r="1421">
       <c r="A1421" t="str">
-        <v>SOEPELE LASKABEL</v>
+        <v>SOFILTRA</v>
       </c>
     </row>
     <row r="1422">
       <c r="A1422" t="str">
-        <v>SOFILTRA</v>
+        <v>SOFIMA</v>
       </c>
     </row>
     <row r="1423">
       <c r="A1423" t="str">
-        <v>SOFIMA</v>
+        <v>SOG</v>
       </c>
     </row>
     <row r="1424">
       <c r="A1424" t="str">
-        <v>SOG</v>
+        <v>SOGEDAC</v>
       </c>
     </row>
     <row r="1425">
       <c r="A1425" t="str">
-        <v>SOGEDAC</v>
+        <v>SOLID TYRE</v>
       </c>
     </row>
     <row r="1426">
       <c r="A1426" t="str">
-        <v>SOLID TYRE</v>
+        <v>SONDA BRITVA</v>
       </c>
     </row>
     <row r="1427">
       <c r="A1427" t="str">
-        <v>SONDA BRITVA</v>
+        <v>SONG CHUAN</v>
       </c>
     </row>
     <row r="1428">
       <c r="A1428" t="str">
-        <v>SONG CHUAN</v>
+        <v>SONNENSCHEIN</v>
       </c>
     </row>
     <row r="1429">
       <c r="A1429" t="str">
-        <v>SONNENSCHEIN</v>
+        <v>SOOSUNG</v>
       </c>
     </row>
     <row r="1430">
       <c r="A1430" t="str">
-        <v>SOOSUNG</v>
+        <v>SOUTHCO</v>
       </c>
     </row>
     <row r="1431">
       <c r="A1431" t="str">
-        <v>SOUTHCO</v>
+        <v>SOVAM</v>
       </c>
     </row>
     <row r="1432">
       <c r="A1432" t="str">
-        <v>SOVAM</v>
+        <v>SPAL</v>
       </c>
     </row>
     <row r="1433">
       <c r="A1433" t="str">
-        <v>SPAL</v>
+        <v>SPAREX</v>
       </c>
     </row>
     <row r="1434">
       <c r="A1434" t="str">
-        <v>SPAREX</v>
+        <v>SPE</v>
       </c>
     </row>
     <row r="1435">
       <c r="A1435" t="str">
-        <v>SPE</v>
+        <v>SPEAKER</v>
       </c>
     </row>
     <row r="1436">
       <c r="A1436" t="str">
-        <v>SPEAKER</v>
+        <v>SPECTROL</v>
       </c>
     </row>
     <row r="1437">
       <c r="A1437" t="str">
-        <v>SPECTROL</v>
+        <v>SPICER</v>
       </c>
     </row>
     <row r="1438">
       <c r="A1438" t="str">
-        <v>SPICER</v>
+        <v>SPIEGEL</v>
       </c>
     </row>
     <row r="1439">
       <c r="A1439" t="str">
-        <v>SPIEGEL</v>
+        <v>SPIJKSTAAL</v>
       </c>
     </row>
     <row r="1440">
       <c r="A1440" t="str">
-        <v>SPIJKSTAAL</v>
+        <v>SPOHN+BURKHARDT</v>
       </c>
     </row>
     <row r="1441">
       <c r="A1441" t="str">
-        <v>SPOHN+BURKHARDT</v>
+        <v>SPRAYMART</v>
       </c>
     </row>
     <row r="1442">
       <c r="A1442" t="str">
-        <v>SPRAYMART</v>
+        <v>SQUARE D</v>
       </c>
     </row>
     <row r="1443">
       <c r="A1443" t="str">
-        <v>SQUARE D</v>
+        <v>SSP KOMPACT</v>
       </c>
     </row>
     <row r="1444">
       <c r="A1444" t="str">
-        <v>SSP KOMPACT</v>
+        <v>STABILUS</v>
       </c>
     </row>
     <row r="1445">
       <c r="A1445" t="str">
-        <v>STABILUS</v>
+        <v>STAGOBEL</v>
       </c>
     </row>
     <row r="1446">
       <c r="A1446" t="str">
-        <v>STAGOBEL</v>
+        <v>STAM</v>
       </c>
     </row>
     <row r="1447">
       <c r="A1447" t="str">
-        <v>STAM</v>
+        <v>STANADYNE</v>
       </c>
     </row>
     <row r="1448">
       <c r="A1448" t="str">
-        <v>STANADYNE</v>
+        <v>STANLEY</v>
       </c>
     </row>
     <row r="1449">
       <c r="A1449" t="str">
-        <v>STANLEY</v>
+        <v>STEFA</v>
       </c>
     </row>
     <row r="1450">
       <c r="A1450" t="str">
-        <v>STEFA</v>
+        <v>STEINBOCK</v>
       </c>
     </row>
     <row r="1451">
       <c r="A1451" t="str">
-        <v>STEINBOCK</v>
+        <v>STELLANA</v>
       </c>
     </row>
     <row r="1452">
       <c r="A1452" t="str">
-        <v>STELLANA</v>
+        <v>STEUTE</v>
       </c>
     </row>
     <row r="1453">
       <c r="A1453" t="str">
-        <v>STEUTE</v>
+        <v>STEYR</v>
       </c>
     </row>
     <row r="1454">
       <c r="A1454" t="str">
-        <v>STEYR</v>
+        <v>STILL</v>
       </c>
     </row>
     <row r="1455">
       <c r="A1455" t="str">
-        <v>STILL</v>
+        <v>STINIS</v>
       </c>
     </row>
     <row r="1456">
       <c r="A1456" t="str">
-        <v>STINIS</v>
+        <v>STOCKA</v>
       </c>
     </row>
     <row r="1457">
       <c r="A1457" t="str">
-        <v>STOCKA</v>
+        <v>STOCKLIN</v>
       </c>
     </row>
     <row r="1458">
       <c r="A1458" t="str">
-        <v>STOCKLIN</v>
+        <v>STOLZENBERG</v>
       </c>
     </row>
     <row r="1459">
       <c r="A1459" t="str">
-        <v>STOLZENBERG</v>
+        <v>STX BEPCO</v>
       </c>
     </row>
     <row r="1460">
       <c r="A1460" t="str">
-        <v>STX BEPCO</v>
+        <v>SU</v>
       </c>
     </row>
     <row r="1461">
       <c r="A1461" t="str">
-        <v>SU</v>
+        <v>SUCO</v>
       </c>
     </row>
     <row r="1462">
       <c r="A1462" t="str">
-        <v>SUCO</v>
+        <v>SUMITOMO</v>
       </c>
     </row>
     <row r="1463">
       <c r="A1463" t="str">
-        <v>SUMITOMO</v>
+        <v>SUNON</v>
       </c>
     </row>
     <row r="1464">
       <c r="A1464" t="str">
-        <v>SUNON</v>
+        <v>SUNWARD</v>
       </c>
     </row>
     <row r="1465">
       <c r="A1465" t="str">
-        <v>SUNWARD</v>
+        <v>SUSPA</v>
       </c>
     </row>
     <row r="1466">
       <c r="A1466" t="str">
-        <v>SUSPA</v>
+        <v>SVETRUCK</v>
       </c>
     </row>
     <row r="1467">
       <c r="A1467" t="str">
-        <v>SVETRUCK</v>
+        <v>SWF</v>
       </c>
     </row>
     <row r="1468">
       <c r="A1468" t="str">
-        <v>SWF</v>
+        <v>Symta-pièces</v>
       </c>
     </row>
     <row r="1469">
       <c r="A1469" t="str">
-        <v>Symta-pièces</v>
+        <v>SYNCHRO-START</v>
       </c>
     </row>
     <row r="1470">
       <c r="A1470" t="str">
-        <v>SYNCHRO-START</v>
+        <v>SYNCLEAN</v>
       </c>
     </row>
     <row r="1471">
       <c r="A1471" t="str">
-        <v>SYNCLEAN</v>
+        <v>SYNFLEX</v>
       </c>
     </row>
     <row r="1472">
       <c r="A1472" t="str">
-        <v>SYNFLEX</v>
+        <v>SØRENSEN</v>
       </c>
     </row>
     <row r="1473">
       <c r="A1473" t="str">
-        <v>SØRENSEN</v>
+        <v>Taif</v>
       </c>
     </row>
     <row r="1474">
       <c r="A1474" t="str">
-        <v>Taif</v>
+        <v>TAIHO</v>
       </c>
     </row>
     <row r="1475">
       <c r="A1475" t="str">
-        <v>TAIHO</v>
+        <v>TAILIFT</v>
       </c>
     </row>
     <row r="1476">
       <c r="A1476" t="str">
-        <v>TAILIFT</v>
+        <v>TAKEUCHI</v>
       </c>
     </row>
     <row r="1477">
       <c r="A1477" t="str">
-        <v>TAKEUCHI</v>
+        <v>TAMA</v>
       </c>
     </row>
     <row r="1478">
       <c r="A1478" t="str">
-        <v>TAMA</v>
+        <v>TAMARRI</v>
       </c>
     </row>
     <row r="1479">
       <c r="A1479" t="str">
-        <v>TAMARRI</v>
+        <v>TASKI</v>
       </c>
     </row>
     <row r="1480">
       <c r="A1480" t="str">
-        <v>TASKI</v>
+        <v>TaurAuto</v>
       </c>
     </row>
     <row r="1481">
       <c r="A1481" t="str">
-        <v>TaurAuto</v>
+        <v>TAYLOR</v>
       </c>
     </row>
     <row r="1482">
       <c r="A1482" t="str">
-        <v>TAYLOR</v>
+        <v>TAYLOR-DUNN</v>
       </c>
     </row>
     <row r="1483">
       <c r="A1483" t="str">
-        <v>TAYLOR-DUNN</v>
+        <v>TCM</v>
       </c>
     </row>
     <row r="1484">
       <c r="A1484" t="str">
-        <v>TCM</v>
+        <v>TCR-NL</v>
       </c>
     </row>
     <row r="1485">
       <c r="A1485" t="str">
-        <v>TCR-NL</v>
+        <v>TECALEMIT</v>
       </c>
     </row>
     <row r="1486">
       <c r="A1486" t="str">
-        <v>TECALEMIT</v>
+        <v>TECH</v>
       </c>
     </row>
     <row r="1487">
       <c r="A1487" t="str">
-        <v>TECH</v>
+        <v>TECHNE</v>
       </c>
     </row>
     <row r="1488">
       <c r="A1488" t="str">
-        <v>TECHNE</v>
+        <v>TECNA</v>
       </c>
     </row>
     <row r="1489">
       <c r="A1489" t="str">
-        <v>TECNA</v>
+        <v>TECNOCAR</v>
       </c>
     </row>
     <row r="1490">
       <c r="A1490" t="str">
-        <v>TECNOCAR</v>
+        <v>TECNOKIT</v>
       </c>
     </row>
     <row r="1491">
       <c r="A1491" t="str">
-        <v>TECNOKIT</v>
+        <v>TECNORD</v>
       </c>
     </row>
     <row r="1492">
       <c r="A1492" t="str">
-        <v>TECNORD</v>
+        <v>TECREEL</v>
       </c>
     </row>
     <row r="1493">
       <c r="A1493" t="str">
-        <v>TECREEL</v>
+        <v>TEHOFILTER</v>
       </c>
     </row>
     <row r="1494">
       <c r="A1494" t="str">
-        <v>TEHOFILTER</v>
+        <v>TELECO</v>
       </c>
     </row>
     <row r="1495">
       <c r="A1495" t="str">
-        <v>TELECO</v>
+        <v>TELEMECANIQUE</v>
       </c>
     </row>
     <row r="1496">
       <c r="A1496" t="str">
-        <v>TELEMECANIQUE</v>
+        <v>TELLURE ROTA</v>
       </c>
     </row>
     <row r="1497">
       <c r="A1497" t="str">
-        <v>TELLURE ROTA</v>
+        <v>TELWIN</v>
       </c>
     </row>
     <row r="1498">
       <c r="A1498" t="str">
-        <v>TELWIN</v>
+        <v>TEM</v>
       </c>
     </row>
     <row r="1499">
       <c r="A1499" t="str">
-        <v>TEM</v>
+        <v>TEMEL</v>
       </c>
     </row>
     <row r="1500">
       <c r="A1500" t="str">
-        <v>TEMEL</v>
+        <v>TEMG</v>
       </c>
     </row>
     <row r="1501">
       <c r="A1501" t="str">
-        <v>TEMG</v>
+        <v>TEND</v>
       </c>
     </row>
     <row r="1502">
       <c r="A1502" t="str">
-        <v>TEND</v>
+        <v>TENNANT</v>
       </c>
     </row>
     <row r="1503">
       <c r="A1503" t="str">
-        <v>TENNANT</v>
+        <v>Teplostar</v>
       </c>
     </row>
     <row r="1504">
       <c r="A1504" t="str">
-        <v>Teplostar</v>
+        <v>TERBERG</v>
       </c>
     </row>
     <row r="1505">
       <c r="A1505" t="str">
-        <v>TERBERG</v>
+        <v>TEREX</v>
       </c>
     </row>
     <row r="1506">
       <c r="A1506" t="str">
-        <v>TEREX</v>
+        <v>TEREX AERIALS</v>
       </c>
     </row>
     <row r="1507">
       <c r="A1507" t="str">
-        <v>TEREX AERIALS</v>
+        <v>TEROSON</v>
       </c>
     </row>
     <row r="1508">
       <c r="A1508" t="str">
-        <v>TEROSON</v>
+        <v>TESCH SYSTEM</v>
       </c>
     </row>
     <row r="1509">
       <c r="A1509" t="str">
-        <v>TESCH SYSTEM</v>
+        <v>TEU FORKLIFT</v>
       </c>
     </row>
     <row r="1510">
       <c r="A1510" t="str">
-        <v>TEU FORKLIFT</v>
+        <v>TEUPEN</v>
       </c>
     </row>
     <row r="1511">
       <c r="A1511" t="str">
-        <v>TEUPEN</v>
+        <v>TEVEMA</v>
       </c>
     </row>
     <row r="1512">
       <c r="A1512" t="str">
-        <v>TEVEMA</v>
+        <v>TEXTAR</v>
       </c>
     </row>
     <row r="1513">
       <c r="A1513" t="str">
-        <v>TEXTAR</v>
+        <v>TFN</v>
       </c>
     </row>
     <row r="1514">
       <c r="A1514" t="str">
-        <v>TFN</v>
+        <v>THALER</v>
       </c>
     </row>
     <row r="1515">
       <c r="A1515" t="str">
-        <v>THALER</v>
+        <v>THERMOKING</v>
       </c>
     </row>
     <row r="1516">
       <c r="A1516" t="str">
-        <v>THERMOKING</v>
+        <v>THK</v>
       </c>
     </row>
     <row r="1517">
       <c r="A1517" t="str">
-        <v>THK</v>
+        <v>THOMAS</v>
       </c>
     </row>
     <row r="1518">
       <c r="A1518" t="str">
-        <v>THOMAS</v>
+        <v>THOROUGHBRED</v>
       </c>
     </row>
     <row r="1519">
       <c r="A1519" t="str">
-        <v>THOROUGHBRED</v>
+        <v>THRIGE-TITAN</v>
       </c>
     </row>
     <row r="1520">
       <c r="A1520" t="str">
-        <v>THRIGE-TITAN</v>
+        <v>THWAITES</v>
       </c>
     </row>
     <row r="1521">
       <c r="A1521" t="str">
-        <v>THWAITES</v>
+        <v>TIANCHENG</v>
       </c>
     </row>
     <row r="1522">
       <c r="A1522" t="str">
-        <v>TIANCHENG</v>
+        <v>TIANZHUI</v>
       </c>
     </row>
     <row r="1523">
       <c r="A1523" t="str">
-        <v>TIANZHUI</v>
+        <v>TIMKEN</v>
       </c>
     </row>
     <row r="1524">
       <c r="A1524" t="str">
-        <v>TIMKEN</v>
+        <v>Tirsan</v>
       </c>
     </row>
     <row r="1525">
       <c r="A1525" t="str">
-        <v>Tirsan</v>
+        <v>TLD</v>
       </c>
     </row>
     <row r="1526">
       <c r="A1526" t="str">
-        <v>TLD</v>
+        <v>TLPE</v>
       </c>
     </row>
     <row r="1527">
       <c r="A1527" t="str">
-        <v>TLPE</v>
+        <v>TONG MYUNG</v>
       </c>
     </row>
     <row r="1528">
       <c r="A1528" t="str">
-        <v>TONG MYUNG</v>
+        <v>Tongsui</v>
       </c>
     </row>
     <row r="1529">
       <c r="A1529" t="str">
-        <v>Tongsui</v>
+        <v>TONNY</v>
       </c>
     </row>
     <row r="1530">
       <c r="A1530" t="str">
-        <v>TONNY</v>
+        <v>TORO</v>
       </c>
     </row>
     <row r="1531">
       <c r="A1531" t="str">
-        <v>TORO</v>
+        <v>TORRINGTON</v>
       </c>
     </row>
     <row r="1532">
       <c r="A1532" t="str">
-        <v>TORRINGTON</v>
+        <v>TOSHIBA</v>
       </c>
     </row>
     <row r="1533">
       <c r="A1533" t="str">
-        <v>TOSHIBA</v>
+        <v>TOSUC</v>
       </c>
     </row>
     <row r="1534">
       <c r="A1534" t="str">
-        <v>TOSUC</v>
+        <v>TOTAL SOURCE</v>
       </c>
     </row>
     <row r="1535">
       <c r="A1535" t="str">
-        <v>TOTAL SOURCE</v>
+        <v>TOTAL SOURCE AMERICA</v>
       </c>
     </row>
     <row r="1536">
       <c r="A1536" t="str">
-        <v>TOTAL SOURCE AMERICA</v>
+        <v>TOTALLIFTER</v>
       </c>
     </row>
     <row r="1537">
       <c r="A1537" t="str">
-        <v>TOTALLIFTER</v>
+        <v>TOUCAN</v>
       </c>
     </row>
     <row r="1538">
       <c r="A1538" t="str">
-        <v>TOUCAN</v>
+        <v>TOVI</v>
       </c>
     </row>
     <row r="1539">
       <c r="A1539" t="str">
-        <v>TOVI</v>
+        <v>TOYO</v>
       </c>
     </row>
     <row r="1540">
       <c r="A1540" t="str">
-        <v>TOYO</v>
+        <v>TOYOTA</v>
       </c>
     </row>
     <row r="1541">
       <c r="A1541" t="str">
-        <v>TOYOTA</v>
+        <v>TP</v>
       </c>
     </row>
     <row r="1542">
       <c r="A1542" t="str">
-        <v>TP</v>
+        <v>TRACK PARTS</v>
       </c>
     </row>
     <row r="1543">
       <c r="A1543" t="str">
-        <v>TRACK PARTS</v>
+        <v>TRACMA</v>
       </c>
     </row>
     <row r="1544">
       <c r="A1544" t="str">
-        <v>TRACMA</v>
+        <v>TRANSPALLETTEN</v>
       </c>
     </row>
     <row r="1545">
       <c r="A1545" t="str">
-        <v>TRANSPALLETTEN</v>
+        <v>TRANSPORT</v>
       </c>
     </row>
     <row r="1546">
       <c r="A1546" t="str">
-        <v>TRANSPORT</v>
+        <v>TREK CLEANING MACHINES</v>
       </c>
     </row>
     <row r="1547">
       <c r="A1547" t="str">
-        <v>TREK CLEANING MACHINES</v>
+        <v>TREPEL</v>
       </c>
     </row>
     <row r="1548">
       <c r="A1548" t="str">
-        <v>TREPEL</v>
+        <v>TREX PARTS</v>
       </c>
     </row>
     <row r="1549">
       <c r="A1549" t="str">
-        <v>TREX PARTS</v>
+        <v>TRIDON</v>
       </c>
     </row>
     <row r="1550">
       <c r="A1550" t="str">
-        <v>TRIDON</v>
+        <v>TRIONIC</v>
       </c>
     </row>
     <row r="1551">
       <c r="A1551" t="str">
-        <v>TRIONIC</v>
+        <v>TROJAN BATTERY</v>
       </c>
     </row>
     <row r="1552">
       <c r="A1552" t="str">
-        <v>TROJAN BATTERY</v>
+        <v>TROMBE POLI</v>
       </c>
     </row>
     <row r="1553">
       <c r="A1553" t="str">
-        <v>TROMBE POLI</v>
+        <v>TROMBETTA</v>
       </c>
     </row>
     <row r="1554">
       <c r="A1554" t="str">
-        <v>TROMBETTA</v>
+        <v>TRUCKAIDS</v>
       </c>
     </row>
     <row r="1555">
       <c r="A1555" t="str">
-        <v>TRUCKAIDS</v>
+        <v>TRUCK-LITE</v>
       </c>
     </row>
     <row r="1556">
       <c r="A1556" t="str">
-        <v>TRUCK-LITE</v>
+        <v>TRUCKTECHNIC</v>
       </c>
     </row>
     <row r="1557">
       <c r="A1557" t="str">
-        <v>TRUCKTECHNIC</v>
+        <v>TRUMP ALELLA</v>
       </c>
     </row>
     <row r="1558">
       <c r="A1558" t="str">
-        <v>TRUMP ALELLA</v>
+        <v>TRW</v>
       </c>
     </row>
     <row r="1559">
       <c r="A1559" t="str">
-        <v>TRW</v>
+        <v>TSK - SUNTRAC</v>
       </c>
     </row>
     <row r="1560">
       <c r="A1560" t="str">
-        <v>TSK - SUNTRAC</v>
+        <v>TUDOR</v>
       </c>
     </row>
     <row r="1561">
       <c r="A1561" t="str">
-        <v>TUDOR</v>
+        <v>TUG</v>
       </c>
     </row>
     <row r="1562">
       <c r="A1562" t="str">
-        <v>TUG</v>
+        <v>TURNER</v>
       </c>
     </row>
     <row r="1563">
       <c r="A1563" t="str">
-        <v>TURNER</v>
+        <v>TUTHILL</v>
       </c>
     </row>
     <row r="1564">
       <c r="A1564" t="str">
-        <v>TUTHILL</v>
+        <v>TVH</v>
       </c>
     </row>
     <row r="1565">
       <c r="A1565" t="str">
-        <v>TVH</v>
+        <v>TWINFLEX</v>
       </c>
     </row>
     <row r="1566">
       <c r="A1566" t="str">
-        <v>TWINFLEX</v>
+        <v>TYCO</v>
       </c>
     </row>
     <row r="1567">
       <c r="A1567" t="str">
-        <v>TYCO</v>
+        <v>TYRI</v>
       </c>
     </row>
     <row r="1568">
       <c r="A1568" t="str">
-        <v>TYRI</v>
+        <v>U T</v>
       </c>
     </row>
     <row r="1569">
       <c r="A1569" t="str">
-        <v>U T</v>
+        <v>UAZ</v>
       </c>
     </row>
     <row r="1570">
       <c r="A1570" t="str">
-        <v>UAZ</v>
+        <v>UCC</v>
       </c>
     </row>
     <row r="1571">
       <c r="A1571" t="str">
-        <v>UCC</v>
+        <v>UFI FILTER</v>
       </c>
     </row>
     <row r="1572">
       <c r="A1572" t="str">
-        <v>UFI FILTER</v>
+        <v>ULIVIERI</v>
       </c>
     </row>
     <row r="1573">
       <c r="A1573" t="str">
-        <v>ULIVIERI</v>
+        <v>ULTRA - DOWTY</v>
       </c>
     </row>
     <row r="1574">
       <c r="A1574" t="str">
-        <v>ULTRA - DOWTY</v>
+        <v>UN FORKLIFT</v>
       </c>
     </row>
     <row r="1575">
       <c r="A1575" t="str">
-        <v>UN FORKLIFT</v>
+        <v>UNICARRIERS</v>
       </c>
     </row>
     <row r="1576">
       <c r="A1576" t="str">
-        <v>UNICARRIERS</v>
+        <v>UNIPOINT</v>
       </c>
     </row>
     <row r="1577">
       <c r="A1577" t="str">
-        <v>UNIPOINT</v>
+        <v>UNIQUE-LITE</v>
       </c>
     </row>
     <row r="1578">
       <c r="A1578" t="str">
-        <v>UNIQUE-LITE</v>
+        <v>UNITED CONTACT</v>
       </c>
     </row>
     <row r="1579">
       <c r="A1579" t="str">
-        <v>UNITED CONTACT</v>
+        <v>UNITRAC</v>
       </c>
     </row>
     <row r="1580">
       <c r="A1580" t="str">
-        <v>UNITRAC</v>
+        <v>UNITRUCK</v>
       </c>
     </row>
     <row r="1581">
       <c r="A1581" t="str">
-        <v>UNITRUCK</v>
+        <v>Univer</v>
       </c>
     </row>
     <row r="1582">
       <c r="A1582" t="str">
-        <v>Univer</v>
+        <v>UNIVERSAL HOBBIES</v>
       </c>
     </row>
     <row r="1583">
       <c r="A1583" t="str">
-        <v>UNIVERSAL HOBBIES</v>
+        <v>UNIVERSAL MACHINE SO</v>
       </c>
     </row>
     <row r="1584">
       <c r="A1584" t="str">
-        <v>UNIVERSAL MACHINE SO</v>
+        <v>UP LIFTING</v>
       </c>
     </row>
     <row r="1585">
       <c r="A1585" t="str">
-        <v>UP LIFTING</v>
+        <v>UPRIGHT</v>
       </c>
     </row>
     <row r="1586">
       <c r="A1586" t="str">
-        <v>UPRIGHT</v>
+        <v>URB</v>
       </c>
     </row>
     <row r="1587">
       <c r="A1587" t="str">
-        <v>URB</v>
+        <v>USCO</v>
       </c>
     </row>
     <row r="1588">
       <c r="A1588" t="str">
-        <v>USCO</v>
+        <v>U-SHIN</v>
       </c>
     </row>
     <row r="1589">
       <c r="A1589" t="str">
-        <v>U-SHIN</v>
+        <v>UTILEV</v>
       </c>
     </row>
     <row r="1590">
       <c r="A1590" t="str">
-        <v>UTILEV</v>
+        <v>UZM</v>
       </c>
     </row>
     <row r="1591">
       <c r="A1591" t="str">
-        <v>UZM</v>
+        <v>VALEO</v>
       </c>
     </row>
     <row r="1592">
       <c r="A1592" t="str">
-        <v>VALEO</v>
+        <v>VALMET</v>
       </c>
     </row>
     <row r="1593">
       <c r="A1593" t="str">
-        <v>VALMET</v>
+        <v>VALON</v>
       </c>
     </row>
     <row r="1594">
       <c r="A1594" t="str">
-        <v>VALON</v>
+        <v>VALTEK</v>
       </c>
     </row>
     <row r="1595">
       <c r="A1595" t="str">
-        <v>VALTEK</v>
+        <v>VALTRA</v>
       </c>
     </row>
     <row r="1596">
       <c r="A1596" t="str">
-        <v>VALTRA</v>
+        <v>VANGENT</v>
       </c>
     </row>
     <row r="1597">
       <c r="A1597" t="str">
-        <v>VANGENT</v>
+        <v>VAPO</v>
       </c>
     </row>
     <row r="1598">
       <c r="A1598" t="str">
-        <v>VAPO</v>
+        <v>VAPORMATIC</v>
       </c>
     </row>
     <row r="1599">
       <c r="A1599" t="str">
-        <v>VAPORMATIC</v>
+        <v>VAPSINT</v>
       </c>
     </row>
     <row r="1600">
       <c r="A1600" t="str">
-        <v>VAPSINT</v>
+        <v>VARIOFIT</v>
       </c>
     </row>
     <row r="1601">
       <c r="A1601" t="str">
-        <v>VARIOFIT</v>
+        <v>VARTA</v>
       </c>
     </row>
     <row r="1602">
       <c r="A1602" t="str">
-        <v>VARTA</v>
+        <v>VCI</v>
       </c>
     </row>
     <row r="1603">
       <c r="A1603" t="str">
-        <v>VCI</v>
+        <v>VDO</v>
       </c>
     </row>
     <row r="1604">
       <c r="A1604" t="str">
-        <v>VDO</v>
+        <v>VEILIGHEID</v>
       </c>
     </row>
     <row r="1605">
       <c r="A1605" t="str">
-        <v>VEILIGHEID</v>
+        <v>VELJAN</v>
       </c>
     </row>
     <row r="1606">
       <c r="A1606" t="str">
-        <v>VELJAN</v>
+        <v>VERIGA</v>
       </c>
     </row>
     <row r="1607">
       <c r="A1607" t="str">
-        <v>VERIGA</v>
+        <v>VERTIMAC</v>
       </c>
     </row>
     <row r="1608">
       <c r="A1608" t="str">
-        <v>VERTIMAC</v>
+        <v>VIBO</v>
       </c>
     </row>
     <row r="1609">
       <c r="A1609" t="str">
-        <v>VIBO</v>
+        <v>VICKERS</v>
       </c>
     </row>
     <row r="1610">
       <c r="A1610" t="str">
-        <v>VICKERS</v>
+        <v>VICTOR REINZ</v>
       </c>
     </row>
     <row r="1611">
       <c r="A1611" t="str">
-        <v>VICTOR REINZ</v>
+        <v>VICTORY</v>
       </c>
     </row>
     <row r="1612">
       <c r="A1612" t="str">
-        <v>VICTORY</v>
+        <v>VICTRON</v>
       </c>
     </row>
     <row r="1613">
       <c r="A1613" t="str">
-        <v>VICTRON</v>
+        <v>VIPER</v>
       </c>
     </row>
     <row r="1614">
       <c r="A1614" t="str">
-        <v>VIPER</v>
+        <v>VIRGIS</v>
       </c>
     </row>
     <row r="1615">
       <c r="A1615" t="str">
-        <v>VIRGIS</v>
+        <v>VIS HYDRAULICS</v>
       </c>
     </row>
     <row r="1616">
       <c r="A1616" t="str">
-        <v>VIS HYDRAULICS</v>
+        <v>VISHAY</v>
       </c>
     </row>
     <row r="1617">
       <c r="A1617" t="str">
-        <v>VISHAY</v>
+        <v>VISION ALERT</v>
       </c>
     </row>
     <row r="1618">
       <c r="A1618" t="str">
-        <v>VISION ALERT</v>
+        <v>VKP</v>
       </c>
     </row>
     <row r="1619">
       <c r="A1619" t="str">
-        <v>VKP</v>
+        <v>VM</v>
       </c>
     </row>
     <row r="1620">
       <c r="A1620" t="str">
-        <v>VM</v>
+        <v>VMAX</v>
       </c>
     </row>
     <row r="1621">
       <c r="A1621" t="str">
-        <v>VMAX</v>
+        <v>VMH MATERIALS</v>
       </c>
     </row>
     <row r="1622">
       <c r="A1622" t="str">
-        <v>VMH MATERIALS</v>
+        <v>VOITH</v>
       </c>
     </row>
     <row r="1623">
       <c r="A1623" t="str">
-        <v>VOITH</v>
+        <v>VOLK</v>
       </c>
     </row>
     <row r="1624">
       <c r="A1624" t="str">
-        <v>VOLK</v>
+        <v>VOLKSWAGEN</v>
       </c>
     </row>
     <row r="1625">
       <c r="A1625" t="str">
-        <v>VOLKSWAGEN</v>
+        <v>VOLVO</v>
       </c>
     </row>
     <row r="1626">
       <c r="A1626" t="str">
-        <v>VOLVO</v>
+        <v>VORWERK</v>
       </c>
     </row>
     <row r="1627">
       <c r="A1627" t="str">
-        <v>VORWERK</v>
+        <v>V-RIEM AFMETING</v>
       </c>
     </row>
     <row r="1628">
       <c r="A1628" t="str">
-        <v>V-RIEM AFMETING</v>
+        <v>VULKOPRIN</v>
       </c>
     </row>
     <row r="1629">
       <c r="A1629" t="str">
-        <v>VULKOPRIN</v>
+        <v>WABASH</v>
       </c>
     </row>
     <row r="1630">
       <c r="A1630" t="str">
-        <v>WABASH</v>
+        <v>WABCO</v>
       </c>
     </row>
     <row r="1631">
       <c r="A1631" t="str">
-        <v>WABCO</v>
+        <v>WACKER NEUSON</v>
       </c>
     </row>
     <row r="1632">
       <c r="A1632" t="str">
-        <v>WACKER NEUSON</v>
+        <v>WAGNER</v>
       </c>
     </row>
     <row r="1633">
       <c r="A1633" t="str">
-        <v>WAGNER</v>
+        <v>WAGNER-LOCKHEAD</v>
       </c>
     </row>
     <row r="1634">
       <c r="A1634" t="str">
-        <v>WAGNER-LOCKHEAD</v>
+        <v>WAHLER</v>
       </c>
     </row>
     <row r="1635">
       <c r="A1635" t="str">
-        <v>WAHLER</v>
+        <v>WAI</v>
       </c>
     </row>
     <row r="1636">
       <c r="A1636" t="str">
-        <v>WAI</v>
+        <v>WALSTED</v>
       </c>
     </row>
     <row r="1637">
       <c r="A1637" t="str">
-        <v>WALSTED</v>
+        <v>WALTER MAUSER</v>
       </c>
     </row>
     <row r="1638">
       <c r="A1638" t="str">
-        <v>WALTER MAUSER</v>
+        <v>WALTHER PRAEZISION</v>
       </c>
     </row>
     <row r="1639">
       <c r="A1639" t="str">
-        <v>WALTHER PRAEZISION</v>
+        <v>WALVOIL</v>
       </c>
     </row>
     <row r="1640">
       <c r="A1640" t="str">
-        <v>WALVOIL</v>
+        <v>WANDA</v>
       </c>
     </row>
     <row r="1641">
       <c r="A1641" t="str">
-        <v>WANDA</v>
+        <v>WANG</v>
       </c>
     </row>
     <row r="1642">
       <c r="A1642" t="str">
-        <v>WANG</v>
+        <v>WARFIELD</v>
       </c>
     </row>
     <row r="1643">
       <c r="A1643" t="str">
-        <v>WARFIELD</v>
+        <v>Warman</v>
       </c>
     </row>
     <row r="1644">
       <c r="A1644" t="str">
-        <v>Warman</v>
+        <v>WARNERELECTRIC</v>
       </c>
     </row>
     <row r="1645">
       <c r="A1645" t="str">
-        <v>WARNERELECTRIC</v>
+        <v>Waspo</v>
       </c>
     </row>
     <row r="1646">
       <c r="A1646" t="str">
-        <v>Waspo</v>
+        <v>WEASLER</v>
       </c>
     </row>
     <row r="1647">
       <c r="A1647" t="str">
-        <v>WEASLER</v>
+        <v>WEBASTO</v>
       </c>
     </row>
     <row r="1648">
       <c r="A1648" t="str">
-        <v>WEBASTO</v>
+        <v>WEBER BORSTELS</v>
       </c>
     </row>
     <row r="1649">
       <c r="A1649" t="str">
-        <v>WEBER BORSTELS</v>
+        <v>WEFAPRESS</v>
       </c>
     </row>
     <row r="1650">
       <c r="A1650" t="str">
-        <v>WEFAPRESS</v>
+        <v>WEHRLE</v>
       </c>
     </row>
     <row r="1651">
       <c r="A1651" t="str">
-        <v>WEHRLE</v>
+        <v>Weichai</v>
       </c>
     </row>
     <row r="1652">
       <c r="A1652" t="str">
-        <v>Weichai</v>
+        <v>WEIDEMANN</v>
       </c>
     </row>
     <row r="1653">
       <c r="A1653" t="str">
-        <v>WEIDEMANN</v>
+        <v>WEIDMULLER</v>
       </c>
     </row>
     <row r="1654">
       <c r="A1654" t="str">
-        <v>WEIDMULLER</v>
+        <v>Weifang</v>
       </c>
     </row>
     <row r="1655">
       <c r="A1655" t="str">
-        <v>Weifang</v>
+        <v>Weifang Wangren Machinery</v>
       </c>
     </row>
     <row r="1656">
       <c r="A1656" t="str">
-        <v>Weifang Wangren Machinery</v>
+        <v>WELDON</v>
       </c>
     </row>
     <row r="1657">
       <c r="A1657" t="str">
-        <v>WELDON</v>
+        <v>WEST ALLOY</v>
       </c>
     </row>
     <row r="1658">
       <c r="A1658" t="str">
-        <v>WEST ALLOY</v>
+        <v>WESTINGHOUSE</v>
       </c>
     </row>
     <row r="1659">
       <c r="A1659" t="str">
-        <v>WESTINGHOUSE</v>
+        <v>WHEELS</v>
       </c>
     </row>
     <row r="1660">
       <c r="A1660" t="str">
-        <v>WHEELS</v>
+        <v>WICKE</v>
       </c>
     </row>
     <row r="1661">
       <c r="A1661" t="str">
-        <v>WICKE</v>
+        <v>WICKMANN</v>
       </c>
     </row>
     <row r="1662">
       <c r="A1662" t="str">
-        <v>WICKMANN</v>
+        <v>WIELMOER</v>
       </c>
     </row>
     <row r="1663">
       <c r="A1663" t="str">
-        <v>WIELMOER</v>
+        <v>WIFO</v>
       </c>
     </row>
     <row r="1664">
       <c r="A1664" t="str">
-        <v>WIFO</v>
+        <v>WIHADO</v>
       </c>
     </row>
     <row r="1665">
       <c r="A1665" t="str">
-        <v>WIHADO</v>
+        <v>WIJLHUIZEN</v>
       </c>
     </row>
     <row r="1666">
       <c r="A1666" t="str">
-        <v>WIJLHUIZEN</v>
+        <v>WILLIAMS CONTROLS</v>
       </c>
     </row>
     <row r="1667">
       <c r="A1667" t="str">
-        <v>WILLIAMS CONTROLS</v>
+        <v>WILSON</v>
       </c>
     </row>
     <row r="1668">
       <c r="A1668" t="str">
-        <v>WILSON</v>
+        <v>WINDSOR INDUSTRIES</v>
       </c>
     </row>
     <row r="1669">
       <c r="A1669" t="str">
-        <v>WINDSOR INDUSTRIES</v>
+        <v>WINNER</v>
       </c>
     </row>
     <row r="1670">
       <c r="A1670" t="str">
-        <v>WINNER</v>
+        <v>WIPPERMANN</v>
       </c>
     </row>
     <row r="1671">
       <c r="A1671" t="str">
-        <v>WIPPERMANN</v>
+        <v>WIRAX</v>
       </c>
     </row>
     <row r="1672">
       <c r="A1672" t="str">
-        <v>WIRAX</v>
+        <v>WIRBEL</v>
       </c>
     </row>
     <row r="1673">
       <c r="A1673" t="str">
-        <v>WIRBEL</v>
+        <v>WISE</v>
       </c>
     </row>
     <row r="1674">
       <c r="A1674" t="str">
-        <v>WISE</v>
+        <v>WIX</v>
       </c>
     </row>
     <row r="1675">
       <c r="A1675" t="str">
-        <v>WIX</v>
+        <v>WM</v>
       </c>
     </row>
     <row r="1676">
       <c r="A1676" t="str">
-        <v>WM</v>
+        <v>WOODAUTO</v>
       </c>
     </row>
     <row r="1677">
       <c r="A1677" t="str">
-        <v>WOODAUTO</v>
+        <v>WOODGATE</v>
       </c>
     </row>
     <row r="1678">
       <c r="A1678" t="str">
-        <v>WOODGATE</v>
+        <v>WOODWARD</v>
       </c>
     </row>
     <row r="1679">
       <c r="A1679" t="str">
-        <v>WOODWARD</v>
+        <v>WURTH</v>
       </c>
     </row>
     <row r="1680">
       <c r="A1680" t="str">
-        <v>WURTH</v>
+        <v>X</v>
       </c>
     </row>
     <row r="1681">
       <c r="A1681" t="str">
-        <v>X</v>
+        <v>XCMG</v>
       </c>
     </row>
     <row r="1682">
       <c r="A1682" t="str">
-        <v>XCMG</v>
+        <v>Xenite</v>
       </c>
     </row>
     <row r="1683">
       <c r="A1683" t="str">
-        <v>Xenite</v>
+        <v>XILIN</v>
       </c>
     </row>
     <row r="1684">
       <c r="A1684" t="str">
-        <v>XILIN</v>
+        <v>XINCHAI</v>
       </c>
     </row>
     <row r="1685">
       <c r="A1685" t="str">
-        <v>XINCHAI</v>
+        <v>XINGYU</v>
       </c>
     </row>
     <row r="1686">
       <c r="A1686" t="str">
-        <v>XINGYU</v>
+        <v>YALE</v>
       </c>
     </row>
     <row r="1687">
       <c r="A1687" t="str">
-        <v>YALE</v>
+        <v>YAMAHA</v>
       </c>
     </row>
     <row r="1688">
       <c r="A1688" t="str">
-        <v>YAMAHA</v>
+        <v>YAMAHA GOLF CAR</v>
       </c>
     </row>
     <row r="1689">
       <c r="A1689" t="str">
-        <v>YAMAHA GOLF CAR</v>
+        <v>YMZ</v>
       </c>
     </row>
     <row r="1690">
       <c r="A1690" t="str">
-        <v>YMZ</v>
+        <v>YANG</v>
       </c>
     </row>
     <row r="1691">
       <c r="A1691" t="str">
-        <v>YANG</v>
+        <v>YANMAR</v>
       </c>
     </row>
     <row r="1692">
       <c r="A1692" t="str">
-        <v>YANMAR</v>
+        <v>YANTAI</v>
       </c>
     </row>
     <row r="1693">
       <c r="A1693" t="str">
-        <v>YANTAI</v>
+        <v>YAZAKI</v>
       </c>
     </row>
     <row r="1694">
       <c r="A1694" t="str">
-        <v>YAZAKI</v>
+        <v>YEC</v>
       </c>
     </row>
     <row r="1695">
       <c r="A1695" t="str">
-        <v>YEC</v>
+        <v>YI JEONG</v>
       </c>
     </row>
     <row r="1696">
       <c r="A1696" t="str">
-        <v>YI JEONG</v>
+        <v>YOUNG LIGHTING</v>
       </c>
     </row>
     <row r="1697">
       <c r="A1697" t="str">
-        <v>YOUNG LIGHTING</v>
+        <v>YOUNGMAN</v>
       </c>
     </row>
     <row r="1698">
       <c r="A1698" t="str">
-        <v>YOUNGMAN</v>
+        <v>YQS</v>
       </c>
     </row>
     <row r="1699">
       <c r="A1699" t="str">
-        <v>YQS</v>
+        <v>YTO</v>
       </c>
     </row>
     <row r="1700">
       <c r="A1700" t="str">
-        <v>YTO</v>
+        <v>YUCHAI</v>
       </c>
     </row>
     <row r="1701">
       <c r="A1701" t="str">
-        <v>YUCHAI</v>
+        <v>YUEH JYH</v>
       </c>
     </row>
     <row r="1702">
       <c r="A1702" t="str">
-        <v>YUEH JYH</v>
+        <v>ZAPI</v>
       </c>
     </row>
     <row r="1703">
       <c r="A1703" t="str">
-        <v>ZAPI</v>
+        <v>ZELO</v>
       </c>
     </row>
     <row r="1704">
       <c r="A1704" t="str">
-        <v>ZELO</v>
+        <v>ZEPPELIN</v>
       </c>
     </row>
     <row r="1705">
       <c r="A1705" t="str">
-        <v>ZEPPELIN</v>
+        <v>ZEPRO</v>
       </c>
     </row>
     <row r="1706">
       <c r="A1706" t="str">
-        <v>ZEPRO</v>
+        <v>ZESKANTENWIELBOUT</v>
       </c>
     </row>
     <row r="1707">
       <c r="A1707" t="str">
-        <v>ZESKANTENWIELBOUT</v>
+        <v>ZETOR</v>
       </c>
     </row>
     <row r="1708">
       <c r="A1708" t="str">
-        <v>ZETOR</v>
+        <v>ZETTLER</v>
       </c>
     </row>
     <row r="1709">
       <c r="A1709" t="str">
-        <v>ZETTLER</v>
+        <v>ZEXEL</v>
       </c>
     </row>
     <row r="1710">
       <c r="A1710" t="str">
-        <v>ZEXEL</v>
+        <v>ZF</v>
       </c>
     </row>
     <row r="1711">
       <c r="A1711" t="str">
-        <v>ZF</v>
+        <v>ZIE 277 (SAXBY)</v>
       </c>
     </row>
     <row r="1712">
       <c r="A1712" t="str">
-        <v>ZIE 277 (SAXBY)</v>
+        <v>ZIL</v>
       </c>
     </row>
     <row r="1713">
       <c r="A1713" t="str">
-        <v>ZIL</v>
+        <v>ZIVAN</v>
       </c>
     </row>
     <row r="1714">
       <c r="A1714" t="str">
-        <v>ZIVAN</v>
+        <v>ZOOMLION</v>
       </c>
     </row>
     <row r="1715">
       <c r="A1715" t="str">
-        <v>ZOOMLION</v>
-      </c>
-    </row>
-    <row r="1716">
-      <c r="A1716" t="str">
         <v>ZTD</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A1716"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A1715"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/import_template.xlsx
+++ b/import_template.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A1752"/>
+  <dimension ref="A1:A1753"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9144,27 +9144,32 @@
     </row>
     <row r="1749">
       <c r="A1749" t="str">
-        <v>ZOOMLION</v>
+        <v>ZMZ</v>
       </c>
     </row>
     <row r="1750">
       <c r="A1750" t="str">
-        <v>ZTD</v>
+        <v>ZOOMLION</v>
       </c>
     </row>
     <row r="1751">
       <c r="A1751" t="str">
-        <v>ZUBR</v>
+        <v>ZTD</v>
       </c>
     </row>
     <row r="1752">
       <c r="A1752" t="str">
+        <v>ZUBR</v>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="str">
         <v>ZVER</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A1752"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A1753"/>
   </ignoredErrors>
 </worksheet>
 </file>